--- a/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
@@ -3227,6 +3227,63 @@
         <v/>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled DS (for DSRA)</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Based on straight-line amort</t>
+        </is>
+      </c>
+      <c r="E93" s="18">
+        <f>MAX(0,$D$57-(1-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="F93" s="18">
+        <f>MAX(0,$D$57-(2-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="G93" s="18">
+        <f>MAX(0,$D$57-(3-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="H93" s="18">
+        <f>MAX(0,$D$57-(4-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="I93" s="18">
+        <f>MAX(0,$D$57-(5-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="J93" s="18">
+        <f>MAX(0,$D$57-(6-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="K93" s="18">
+        <f>MAX(0,$D$57-(7-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="L93" s="18">
+        <f>MAX(0,$D$57-(8-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="M93" s="18">
+        <f>MAX(0,$D$57-(9-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="N93" s="18">
+        <f>MAX(0,$D$57-(10-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+    </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
@@ -3260,47 +3317,47 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Next Yr DS × DSRA Months / 12</t>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
         </is>
       </c>
       <c r="D95" s="18">
-        <f>E87*$D$45/12</f>
+        <f>E93*$D$45/12</f>
         <v/>
       </c>
       <c r="E95" s="18">
-        <f>F87*$D$45/12</f>
+        <f>F93*$D$45/12</f>
         <v/>
       </c>
       <c r="F95" s="18">
-        <f>G87*$D$45/12</f>
+        <f>G93*$D$45/12</f>
         <v/>
       </c>
       <c r="G95" s="18">
-        <f>H87*$D$45/12</f>
+        <f>H93*$D$45/12</f>
         <v/>
       </c>
       <c r="H95" s="18">
-        <f>I87*$D$45/12</f>
+        <f>I93*$D$45/12</f>
         <v/>
       </c>
       <c r="I95" s="18">
-        <f>J87*$D$45/12</f>
+        <f>J93*$D$45/12</f>
         <v/>
       </c>
       <c r="J95" s="18">
-        <f>K87*$D$45/12</f>
+        <f>K93*$D$45/12</f>
         <v/>
       </c>
       <c r="K95" s="18">
-        <f>L87*$D$45/12</f>
+        <f>L93*$D$45/12</f>
         <v/>
       </c>
       <c r="L95" s="18">
-        <f>M87*$D$45/12</f>
+        <f>M93*$D$45/12</f>
         <v/>
       </c>
       <c r="M95" s="18">
-        <f>N87*$D$45/12</f>
+        <f>N93*$D$45/12</f>
         <v/>
       </c>
       <c r="N95" s="18">

--- a/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
@@ -2190,43 +2190,43 @@
         </is>
       </c>
       <c r="E70" s="18">
-        <f>$D$56*$D$24*E64/1000000000</f>
+        <f>$D$56*$D$24*E64/1E9</f>
         <v/>
       </c>
       <c r="F70" s="18">
-        <f>$D$56*$D$24*F64/1000000000</f>
+        <f>$D$56*$D$24*F64/1E9</f>
         <v/>
       </c>
       <c r="G70" s="18">
-        <f>$D$56*$D$24*G64/1000000000</f>
+        <f>$D$56*$D$24*G64/1E9</f>
         <v/>
       </c>
       <c r="H70" s="18">
-        <f>$D$56*$D$24*H64/1000000000</f>
+        <f>$D$56*$D$24*H64/1E9</f>
         <v/>
       </c>
       <c r="I70" s="18">
-        <f>$D$56*$D$24*I64/1000000000</f>
+        <f>$D$56*$D$24*I64/1E9</f>
         <v/>
       </c>
       <c r="J70" s="18">
-        <f>$D$56*$D$24*J64/1000000000</f>
+        <f>$D$56*$D$24*J64/1E9</f>
         <v/>
       </c>
       <c r="K70" s="18">
-        <f>$D$56*$D$24*K64/1000000000</f>
+        <f>$D$56*$D$24*K64/1E9</f>
         <v/>
       </c>
       <c r="L70" s="18">
-        <f>$D$56*$D$24*L64/1000000000</f>
+        <f>$D$56*$D$24*L64/1E9</f>
         <v/>
       </c>
       <c r="M70" s="18">
-        <f>$D$56*$D$24*M64/1000000000</f>
+        <f>$D$56*$D$24*M64/1E9</f>
         <v/>
       </c>
       <c r="N70" s="18">
-        <f>$D$56*$D$24*N64/1000000000</f>
+        <f>$D$56*$D$24*N64/1E9</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
@@ -232,6 +232,46 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lotus Infrastructure</author>
+  </authors>
+  <commentList>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0">
+      <text>
+        <t>Unlike baseload, peakers run only during high-price hours. 400-800 hrs/yr typical. NOT capacity factor × 8760.</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0" shapeId="0">
+      <text>
+        <t>Each start-stop cycle causes wear. Major maintenance every 5-7 years. Factor into cash flow timing.</t>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <t>CRITICAL: Use dispatch hours, NOT CF × 8760. Peakers run few hours but earn most revenue from capacity payments.</t>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0">
+      <text>
+        <t>Each start-stop cycle causes wear. Major maintenance every 5-7 years. Factor into cash flow timing.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -523,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -601,6 +641,11 @@
           <t>More volatile revenue profile than CCGT. Capacity revenues more stable, but energy upside is lumpier. Conservative structure provides cushion.</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Debt / EV</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="23" t="inlineStr"/>
@@ -625,6 +670,11 @@
           <t>CRITICAL: Peakers use dispatch hours (400), NOT capacity factor × 8,760. This is the most common modeling error.</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Hours run per year</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
@@ -649,6 +699,11 @@
           <t>Need to retain cash for major maintenance. HGP (hot gas path) inspection every 5 years is $4mm+.</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>% of excess cash to prepay</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
@@ -659,6 +714,11 @@
       <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Hot gas path inspection - internal combustion parts require overhaul. Must fund from retained cash, not debt.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>One-time major overhaul</t>
         </is>
       </c>
     </row>
@@ -673,6 +733,10 @@
         </is>
       </c>
       <c r="B16" s="27" t="n"/>
+      <c r="C16">
+        <f> Capacity × Dispatch × Avail</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
@@ -709,6 +773,11 @@
         </is>
       </c>
       <c r="B20" s="27" t="n"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>One-time major overhaul</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
@@ -782,8 +851,141 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
@@ -240,34 +240,9 @@
     <author>Lotus Infrastructure</author>
   </authors>
   <commentList>
-    <comment ref="C8" authorId="0" shapeId="0">
-      <text>
-        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0" shapeId="0">
-      <text>
-        <t>Unlike baseload, peakers run only during high-price hours. 400-800 hrs/yr typical. NOT capacity factor × 8760.</t>
-      </text>
-    </comment>
     <comment ref="C13" authorId="0" shapeId="0">
       <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="0" shapeId="0">
-      <text>
-        <t>Each start-stop cycle causes wear. Major maintenance every 5-7 years. Factor into cash flow timing.</t>
-      </text>
-    </comment>
-    <comment ref="C16" authorId="0" shapeId="0">
-      <text>
-        <t>CRITICAL: Use dispatch hours, NOT CF × 8760. Peakers run few hours but earn most revenue from capacity payments.</t>
-      </text>
-    </comment>
-    <comment ref="C20" authorId="0" shapeId="0">
-      <text>
-        <t>Each start-stop cycle causes wear. Major maintenance every 5-7 years. Factor into cash flow timing.</t>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
       </text>
     </comment>
   </commentList>
@@ -641,11 +616,6 @@
           <t>More volatile revenue profile than CCGT. Capacity revenues more stable, but energy upside is lumpier. Conservative structure provides cushion.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Debt / EV</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="23" t="inlineStr"/>
@@ -670,11 +640,6 @@
           <t>CRITICAL: Peakers use dispatch hours (400), NOT capacity factor × 8,760. This is the most common modeling error.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Hours run per year</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
@@ -701,7 +666,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>% of excess cash to prepay</t>
+          <t>MIN(Excess×%, Bal−Sched)</t>
         </is>
       </c>
     </row>
@@ -714,11 +679,6 @@
       <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Hot gas path inspection - internal combustion parts require overhaul. Must fund from retained cash, not debt.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>One-time major overhaul</t>
         </is>
       </c>
     </row>
@@ -733,10 +693,6 @@
         </is>
       </c>
       <c r="B16" s="27" t="n"/>
-      <c r="C16">
-        <f> Capacity × Dispatch × Avail</f>
-        <v/>
-      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
@@ -773,11 +729,6 @@
         </is>
       </c>
       <c r="B20" s="27" t="n"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>One-time major overhaul</t>
-        </is>
-      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="23" t="inlineStr">

--- a/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuition Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +55,13 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000066CC"/>
     </font>
   </fonts>
   <fills count="7">
@@ -111,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,6 +167,8 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -538,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -802,138 +813,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -941,6 +820,257 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: Peaker ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Time: 4 hours | Deliverables: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>SITUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>200 MW peaker in NYISO Zone J at $95mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. What levered IRR at indicative price?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. Downside DSCR under stress?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. Key diligence items?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4. Protections to negotiate?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IC MEMO - COACHING FRAMEWORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>1. EXECUTIVE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>Tip: Lead with IRR and recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>2. TRANSACTION OVERVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>Tip: Sources &amp; uses, debt terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>3. INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>Tip: 3-4 bullets on attractiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>4. KEY RISKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>Tip: Market, operational, regulatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>5. MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>Tip: Hedging, contracts, structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>6. SENSITIVITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>Tip: ±10-20% on key inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>7. RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>Tip: Clear yes/no with walk-away price</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1089,7 +1219,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="30">
-        <f>MIN(E92:K92)</f>
+        <f>IF(COUNTIF(E92:K92,"&gt;0")&gt;0,MINIFS(E92:K92,E92:K92,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuition Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,6 +169,12 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -243,21 +249,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Lotus Infrastructure</author>
-  </authors>
-  <commentList>
-    <comment ref="C13" authorId="0" shapeId="0">
-      <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,273 +540,550 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:A94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>PEAKER MODEL - INTUITION GUIDE</t>
-        </is>
-      </c>
-      <c r="B1" s="24" t="inlineStr"/>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="23" t="inlineStr"/>
-      <c r="B2" s="24" t="inlineStr"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>SECTION</t>
-        </is>
-      </c>
-      <c r="B3" s="25" t="inlineStr">
-        <is>
-          <t>WHY IT MATTERS / KEY LOGIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="23" t="inlineStr"/>
-      <c r="B4" s="24" t="inlineStr"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>═══ BUSINESS CONTEXT ═══</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>What is a Peaker?</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>Simple cycle gas turbine - fast-start units that run only during peak demand (~400 hours/year vs 4,800 for CCGT). Less efficient but can start in 10-15 minutes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>Revenue Mix</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>60%+ from capacity payments for being available. Energy revenue is smaller (few running hours) but at high prices (dispatched during peaks).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>Why Lower Leverage (30%)?</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>More volatile revenue profile than CCGT. Capacity revenues more stable, but energy upside is lumpier. Conservative structure provides cushion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="23" t="inlineStr"/>
-      <c r="B9" s="24" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>═══ KEY DIFFERENCES FROM CCGT ═══</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Dispatch Hours vs CF</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>CRITICAL: Peakers use dispatch hours (400), NOT capacity factor × 8,760. This is the most common modeling error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>Heat Rate (10,500 Btu/kWh)</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>Less efficient than CCGT (7,000). Acceptable because fuel cost is small % of revenue - availability matters more.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>Lower Cash Sweep (50%)</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Need to retain cash for major maintenance. HGP (hot gas path) inspection every 5 years is $4mm+.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MIN(Excess×%, Bal−Sched)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>Major Maintenance Y5</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>Hot gas path inspection - internal combustion parts require overhaul. Must fund from retained cash, not debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="23" t="inlineStr"/>
-      <c r="B15" s="24" t="inlineStr"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>═══ GENERATION FORMULA ═══</t>
-        </is>
-      </c>
-      <c r="B16" s="27" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>Correct Formula</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>Generation = Capacity × Dispatch Hours × Availability = 200 MW × 400 hrs × 94% = 75,200 MWh</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>WRONG Formula</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>DO NOT use: Capacity × CF × 8,760. That's for baseload plants, not peakers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="23" t="inlineStr"/>
-      <c r="B19" s="24" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>═══ MAINTENANCE IMPACT ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="27" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>Y5 Cash Flow</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>CFADS drops by $4mm in Y5 due to HGP inspection. This hits DSCR - make sure covenant still passes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>Why Not Debt-Fund Maint?</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>Maintenance is operational expense, not capital. Lenders expect you to fund from operations. That's why sweep is only 50%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="23" t="inlineStr"/>
-      <c r="B23" s="24" t="inlineStr"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>═══ COMMON IC QUESTIONS ═══</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Q: Why is energy price $95/MWh?</t>
-        </is>
-      </c>
-      <c r="B25" s="29" t="inlineStr">
-        <is>
-          <t>Dispatch-weighted average. Peakers only run during high-price hours, so their realized price &gt; average market price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>Q: What's UCAP vs ICAP?</t>
-        </is>
-      </c>
-      <c r="B26" s="29" t="inlineStr">
-        <is>
-          <t>UCAP = Unforced Capacity (adjusted for reliability). ICAP = Installed Capacity (nameplate). Markets pay for UCAP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>Q: Downside if peaker never dispatches?</t>
-        </is>
-      </c>
-      <c r="B27" s="29" t="inlineStr">
-        <is>
-          <t>Still receive capacity payments. Energy revenue is upside, not base case. Worst case = capacity-only revenue.</t>
+    <row r="1">
+      <c r="A1">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>LOTUS INFRASTRUCTURE PARTNERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: SIMPLE CYCLE GAS TURBINE (PEAKER) ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TIME: 4 Hours | DATE: January 2026 | DELIVERABLES: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>--- MODEL TIMELINE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Year 0 (2025): Transaction close Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Year 1 (2026): First full year; start-based maintenance tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Year 5 (2030): Potential hot gas path inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Year 7 (2032): Target exit / debt maturity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Year 10 (2035): Model horizon end</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>--- SITUATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="inlineStr">
+        <is>
+          <t>Lotus Infrastructure Partners is evaluating a 200 MW simple-cycle gas
+turbine peaking facility in NYISO Zone J (New York City). The plant is 8 years
+old with approximately 2,500 equivalent operating starts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>Zone J has strong capacity prices due to transmission constraints. The facility
+provides reliability during summer peaks and winter cold snaps. It operates
+approximately 400 hours per year with revenue heavily weighted to capacity
+payments (~70% of total).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>The 10,500 Btu/kWh heat rate is higher than CCGT but acceptable for peaking
+duty. Recent planning studies indicate potential capacity additions over 3-5
+years including offshore wind and battery storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>The seller is asking $95mm with bids due by January 31, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>--- KEY VALUE DRIVERS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>* Capacity Price: Peakers earn 70%+ of revenue from capacity auctions</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>* Dispatch Hours: Annual run hours drive energy revenue and fuel cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>* Starts: Each start costs money and accelerates maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>* Availability: UCAP derate risk if availability drops below threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>--- STEP-BY-STEP MODEL BUILDING GUIDE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t>STEP-BY-STEP MODEL BUILDING GUIDE FOR PEAKERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="37" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="37" t="inlineStr">
+        <is>
+          <t>KEY DIFFERENCE: Generation = Capacity x Dispatch Hours x Availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>(NOT Capacity x CF x 8,760 like CCGT!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="37" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>1. SET UP INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Capacity: 200 MW</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Heat Rate: 10,500 Btu/kWh (worse than CCGT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Availability: 94% (mechanical availability, not CF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - FOR: 5% (for UCAP derate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Dispatch Hours: 400 hrs/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Starts per Year: ~50-100</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="37" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="37" t="inlineStr">
+        <is>
+          <t>2. BUILD GENERATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Generation = Capacity x Dispatch Hours x Availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   = 200 MW x 400 hrs x 0.94 = 75,200 MWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="37" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="37" t="inlineStr">
+        <is>
+          <t>3. CAPACITY REVENUE IS DOMINANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   UCAP = Capacity x (1 - FOR) = 200 x 0.95 = 190 MW</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Capacity Revenue = UCAP x $/kW-yr x 1000 / 1E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Verify: Capacity should be ~70% of total revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="37" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>4. DEBT STRUCTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   50% cash sweep (vs 75% for CCGT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Preserve flexibility for lumpy maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Peaker cash flows more volatile</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>--- HOW TO AVOID CIRCULARITY ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Same approach as CCGT - use Scheduled DS for DSRA Target to avoid circularity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="34" t="inlineStr">
+        <is>
+          <t>--- ALTERNATIVE SCENARIOS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>A. Ancillary Services Revenue:</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Spinning/non-spinning reserves</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Can be 10-15% of total revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>B. Black Start Capability:</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Premium for grid restoration</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Adds contracted revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C. Capacity Contract vs Merchant:</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Different risk profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Affects debt sizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="34" t="inlineStr">
+        <is>
+          <t>--- QA CHECKS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>QA CHECKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1. Capacity revenue should be 60-75% of total (peaker profile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2. Generation = Dispatch Hours x Availability (NOT CF x 8760)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3. Energy margin may be negative in some hours (heat rate penalty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4. DSCR &gt;= 1.25x during debt tenor</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="34" t="inlineStr">
+        <is>
+          <t>--- HINTS &amp; PITFALLS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="35" t="inlineStr">
+        <is>
+          <t>* Capacity is ~70% of revenue - focus sensitivity there</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="35" t="inlineStr">
+        <is>
+          <t>* Each start costs money plus accelerates maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="35" t="inlineStr">
+        <is>
+          <t>* Zone J premium can erode if storage/transmission added</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="35" t="inlineStr">
+        <is>
+          <t>* Don't model generation as CF x 8760 - use Dispatch Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="34" t="inlineStr">
+        <is>
+          <t>--- INTERVIEW QUESTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Q: How would 100 MW of battery storage in Zone J affect capacity prices?</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Q: Walk me through starts-based vs hours-based maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Q: Why is availability so critical for peaker economics?</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Q: How would you model the revenue mix between capacity and energy?</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1101,38 +1369,60 @@
           <t>Peaker Model - Lotus Infrastructure Partners</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N1" s="2" t="n">
-        <v>10</v>
+      <c r="D1" s="36" t="inlineStr">
+        <is>
+          <t>Y0 (2025)</t>
+        </is>
+      </c>
+      <c r="E1" s="36" t="inlineStr">
+        <is>
+          <t>Y1 (2026)</t>
+        </is>
+      </c>
+      <c r="F1" s="36" t="inlineStr">
+        <is>
+          <t>Y2 (2027)</t>
+        </is>
+      </c>
+      <c r="G1" s="36" t="inlineStr">
+        <is>
+          <t>Y3 (2028)</t>
+        </is>
+      </c>
+      <c r="H1" s="36" t="inlineStr">
+        <is>
+          <t>Y4 (2029)</t>
+        </is>
+      </c>
+      <c r="I1" s="36" t="inlineStr">
+        <is>
+          <t>Y5 (2030)</t>
+        </is>
+      </c>
+      <c r="J1" s="36" t="inlineStr">
+        <is>
+          <t>Y6 (2031)</t>
+        </is>
+      </c>
+      <c r="K1" s="36" t="inlineStr">
+        <is>
+          <t>Y7 (2032)</t>
+        </is>
+      </c>
+      <c r="L1" s="36" t="inlineStr">
+        <is>
+          <t>Y8 (2033)</t>
+        </is>
+      </c>
+      <c r="M1" s="36" t="inlineStr">
+        <is>
+          <t>Y9 (2034)</t>
+        </is>
+      </c>
+      <c r="N1" s="36" t="inlineStr">
+        <is>
+          <t>Y10 (2035)</t>
+        </is>
       </c>
     </row>
     <row r="2">

--- a/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +92,11 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -149,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,6 +232,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -309,7 +315,7 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="A82" authorId="0" shapeId="0">
+    <comment ref="A83" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">SPARK SPREAD
 Profit per MWh after fuel cost.
@@ -3010,7 +3016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N151"/>
+  <dimension ref="A1:N144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3092,46 +3098,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE: Key formulas blanked. Rebuild using Formula Logic hints in Column C. ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>═══ AUDIT STRIP ═══</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Entry EV</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="7">
-        <f>$D$17</f>
-        <v/>
-      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Y1 EBITDA</t>
+          <t>Entry EV</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3141,457 +3137,448 @@
       </c>
       <c r="C4" s="6" t="inlineStr"/>
       <c r="D4" s="7">
-        <f>E75</f>
+        <f>$D$17</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Y1 EBITDA</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>═══════════ CONTROL PANEL ═══════════</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n"/>
-      <c r="C5" s="49" t="n"/>
-      <c r="D5" s="49" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="49" t="n"/>
       <c r="B6" s="49" t="n"/>
       <c r="C6" s="49" t="n"/>
       <c r="D6" s="49" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
+      <c r="A7" s="49" t="n"/>
       <c r="B7" s="49" t="n"/>
       <c r="C7" s="49" t="n"/>
       <c r="D7" s="49" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
+      <c r="A8" s="50" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="B8" s="49" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D8" s="47" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="C8" s="49" t="n"/>
+      <c r="D8" s="49" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
         <is>
-          <t>Contract End Year</t>
+          <t>Revenue Mode</t>
         </is>
       </c>
       <c r="B9" s="49" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
+          <t>Merchant / Contracted / Hybrid</t>
+        </is>
+      </c>
+      <c r="D9" s="47" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B10" s="49" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>0 = pure merchant; else year PPA ends</t>
         </is>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D10" s="47" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="49" t="n"/>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="49" t="n"/>
-    </row>
     <row r="11">
-      <c r="A11" s="50" t="inlineStr">
-        <is>
-          <t>TIMING</t>
-        </is>
-      </c>
+      <c r="A11" s="49" t="n"/>
       <c r="B11" s="49" t="n"/>
       <c r="C11" s="49" t="n"/>
       <c r="D11" s="49" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t>Exit Year</t>
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>TIMING</t>
         </is>
       </c>
       <c r="B12" s="49" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>5 / 7 / 10</t>
-        </is>
-      </c>
-      <c r="D12" s="47" t="n">
-        <v>7</v>
-      </c>
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="49" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
         <is>
-          <t>Tax Credit End Year</t>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B13" s="49" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D13" s="47" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B14" s="49" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
           <t>0 = N/A; else last year of PTC/ITC</t>
         </is>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D14" s="47" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="49" t="n"/>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-    </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
-        <is>
-          <t>DEBT</t>
-        </is>
-      </c>
+      <c r="A15" s="49" t="n"/>
       <c r="B15" s="49" t="n"/>
       <c r="C15" s="49" t="n"/>
-      <c r="D15" s="51" t="n"/>
+      <c r="D15" s="49" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>Debt Sweep</t>
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>DEBT</t>
         </is>
       </c>
       <c r="B16" s="49" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF (for sweep assets)</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+      <c r="C16" s="49" t="n"/>
+      <c r="D16" s="51" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>Sweep %</t>
+          <t>Debt Sweep</t>
         </is>
       </c>
       <c r="B17" s="49" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>Sweep %</t>
+        </is>
+      </c>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
           <t>Active when Sweep = ON</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="49" t="n"/>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="52" t="n"/>
-    </row>
     <row r="19">
-      <c r="A19" s="50" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
+      <c r="A19" s="49" t="n"/>
       <c r="B19" s="49" t="n"/>
       <c r="C19" s="49" t="n"/>
-      <c r="D19" s="53" t="n"/>
+      <c r="D19" s="52" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="53" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Carbon Region</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>None / CARB / RGGI (thermal only)</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D21" s="47" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="54" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="54" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="B21" s="49" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D22" s="47" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="10">
-        <f>D116</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Debt Payoff Y7</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
       <c r="D23" s="10">
-        <f>IF(K91&lt;1,"PASS","FAIL")</f>
+        <f>D116</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Min DSCR ≥ 1.25x</t>
+          <t>Debt Payoff Y7</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr"/>
       <c r="C24" s="6" t="inlineStr"/>
       <c r="D24" s="10">
-        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25"/>
+        <f>IF(K91&lt;1,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Min DSCR ≥ 1.25x</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="10" t="inlineStr"/>
+    </row>
     <row r="26"/>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>TRANSACTION INPUTS</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Entry EV</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Purchase price</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>110</v>
-      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Transaction Fees</t>
+          <t>Entry EV</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Legal, advisory, financing</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="n">
-        <v>0.015</v>
+          <t>Purchase price</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Exit Multiple</t>
+          <t>Transaction Fees</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>On exit year EBITDA</t>
-        </is>
-      </c>
-      <c r="D30" s="33" t="n">
-        <v>7</v>
+          <t>Legal, advisory, financing</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>Exit Multiple</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>On exit year EBITDA</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>Exit Year</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Hold period</t>
         </is>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D32" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>ASSET INPUTS</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n"/>
-      <c r="L33" s="4" t="n"/>
-      <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Capacity</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Nameplate rating</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>200</v>
-      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Heat Rate</t>
+          <t>Capacity</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Btu/kWh</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Less efficient than CCGT</t>
+          <t>Nameplate rating</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>10500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Heat Rate</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Btu/kWh</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>For UCAP accreditation</t>
-        </is>
-      </c>
-      <c r="D36" s="32" t="n">
-        <v>0.9399999999999999</v>
+          <t>Less efficient than CCGT</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>10500</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Forced Outage Rate</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -3601,280 +3588,280 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Unplanned downtime</t>
+          <t>For UCAP accreditation</t>
         </is>
       </c>
       <c r="D37" s="32" t="n">
-        <v>0.05</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>Forced Outage Rate</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Unplanned downtime</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>Dispatch Hours</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>hours/yr</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Peak hours only (~400)</t>
         </is>
       </c>
-      <c r="D38" s="14" t="n">
+      <c r="D39" s="14" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>PRICING INPUTS</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
-      <c r="M40" s="4" t="n"/>
-      <c r="N40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Power Price Y1</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>$/MWh</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Higher (dispatch-weighted)</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>95</v>
-      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Capacity Price Y1</t>
+          <t>Power Price Y1</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr</t>
+          <t>$/MWh</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>ICAP/RPM result</t>
+          <t>Higher (dispatch-weighted)</t>
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Gas Price Y1</t>
+          <t>Capacity Price Y1</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>$/mmBtu</t>
+          <t>$/kW-yr</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Henry Hub + basis</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="n">
-        <v>3.25</v>
+          <t>ICAP/RPM result</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>Gas Price Y1</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>$/mmBtu</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Henry Hub + basis</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>%/yr</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Applied to all prices/costs</t>
         </is>
       </c>
-      <c r="D44" s="32" t="n">
+      <c r="D45" s="32" t="n">
         <v>0.025</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>COST INPUTS</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-      <c r="L46" s="4" t="n"/>
-      <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>VOM</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>$/MWh</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Variable O&amp;M</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="n">
-        <v>4</v>
-      </c>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>FOM</t>
+          <t>VOM</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr</t>
+          <t>$/MWh</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M</t>
+          <t>Variable O&amp;M</t>
         </is>
       </c>
       <c r="D48" s="15" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Major Maintenance Year</t>
+          <t>FOM</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>$/kW-yr</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Hot gas path inspection</t>
-        </is>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>5</v>
+          <t>Fixed O&amp;M</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
+          <t>Major Maintenance Year</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Hot gas path inspection</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>Major Maintenance Cost</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>HGP inspection cost</t>
         </is>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D51" s="11" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>FINANCING INPUTS</t>
         </is>
       </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Leverage</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Debt / Entry EV (lower)</t>
-        </is>
-      </c>
-      <c r="D53" s="32" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Leverage</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -3884,138 +3871,138 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>All-in borrowing cost</t>
+          <t>Debt / Entry EV (lower)</t>
         </is>
       </c>
       <c r="D54" s="32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Debt Tenor</t>
+          <t>Interest Rate</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Amortization period</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="n">
-        <v>7</v>
+          <t>All-in borrowing cost</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>DSRA Months</t>
+          <t>Debt Tenor</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Debt service reserve</t>
+          <t>Amortization period</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep %</t>
+          <t>DSRA Months</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Lower for maint reserves</t>
-        </is>
-      </c>
-      <c r="D57" s="32" t="n">
-        <v>0.5</v>
+          <t>Debt service reserve</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
+          <t>Cash Sweep %</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Lower for maint reserves</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
           <t>Lock-up DSCR</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>Distribution threshold</t>
         </is>
       </c>
-      <c r="D58" s="33" t="n">
+      <c r="D59" s="33" t="n">
         <v>1.1</v>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>TAX INPUTS</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="n"/>
-      <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="n"/>
-      <c r="J60" s="4" t="n"/>
-      <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n"/>
-      <c r="M60" s="4" t="n"/>
-      <c r="N60" s="4" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Tax Rate</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Blended federal + state</t>
-        </is>
-      </c>
-      <c r="D61" s="32" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="4" t="n"/>
+      <c r="N61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Depreciable Basis</t>
+          <t>Tax Rate</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -4025,121 +4012,120 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>% of EV for depreciation</t>
+          <t>Blended federal + state</t>
         </is>
       </c>
       <c r="D62" s="32" t="n">
-        <v>0.85</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
+          <t>Depreciable Basis</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>% of EV for depreciation</t>
+        </is>
+      </c>
+      <c r="D63" s="32" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
           <t>Depreciation Life</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>Straight-line</t>
         </is>
       </c>
-      <c r="D63" s="14" t="n">
+      <c r="D64" s="14" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>CALCULATED ITEMS</t>
         </is>
       </c>
-      <c r="B65" s="4" t="n"/>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="4" t="n"/>
-      <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n"/>
-      <c r="J65" s="4" t="n"/>
-      <c r="K65" s="4" t="n"/>
-      <c r="L65" s="4" t="n"/>
-      <c r="M65" s="4" t="n"/>
-      <c r="N65" s="4" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>UCAP (Unforced Capacity)</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Capacity × (1 - FOR)</t>
-        </is>
-      </c>
-      <c r="D66" s="16">
-        <f>$D$23*(1-$D$26)</f>
-        <v/>
-      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Annual Generation</t>
+          <t>UCAP (Unforced Capacity)</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>MWh</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Capacity × Hours × Avail</t>
-        </is>
-      </c>
-      <c r="D67" s="17">
-        <f>$D$23*$D$27*$D$25</f>
+          <t>Capacity × (1 - FOR)</t>
+        </is>
+      </c>
+      <c r="D67" s="16">
+        <f>$D$23*(1-$D$26)</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Debt Amount</t>
+          <t>Annual Generation</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>MWh</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Entry EV × Leverage</t>
-        </is>
-      </c>
-      <c r="D68" s="18">
-        <f>$D$17*$D$42</f>
+          <t>Capacity × Hours × Avail</t>
+        </is>
+      </c>
+      <c r="D68" s="17">
+        <f>$D$23*$D$27*$D$25</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Annual Depreciation</t>
+          <t>Debt Amount</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -4149,122 +4135,83 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>EV × Basis / Life</t>
+          <t>Entry EV × Leverage</t>
         </is>
       </c>
       <c r="D69" s="18">
-        <f>$D$17*$D$51/$D$52</f>
+        <f>$D$17*$D$42</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
+          <t>Annual Depreciation</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>EV × Basis / Life</t>
+        </is>
+      </c>
+      <c r="D70" s="18">
+        <f>$D$17*$D$51/$D$52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
           <t>Scheduled Principal</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>$mm/yr</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Debt / Tenor</t>
         </is>
       </c>
-      <c r="D70" s="18">
-        <f>$D$57/$D$44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="D71" s="18" t="inlineStr"/>
+    </row>
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>OPERATING MODEL</t>
         </is>
       </c>
-      <c r="B72" s="4" t="n"/>
-      <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n"/>
-      <c r="F72" s="4" t="n"/>
-      <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="n"/>
-      <c r="J72" s="4" t="n"/>
-      <c r="K72" s="4" t="n"/>
-      <c r="L72" s="4" t="n"/>
-      <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Power Price</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>$/MWh</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>Escalated</t>
-        </is>
-      </c>
-      <c r="E73" s="18">
-        <f>$D$30*(1+$D$33)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F73" s="18">
-        <f>$D$30*(1+$D$33)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G73" s="18">
-        <f>$D$30*(1+$D$33)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H73" s="18">
-        <f>$D$30*(1+$D$33)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I73" s="18">
-        <f>$D$30*(1+$D$33)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J73" s="18">
-        <f>$D$30*(1+$D$33)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K73" s="18">
-        <f>$D$30*(1+$D$33)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L73" s="18">
-        <f>$D$30*(1+$D$33)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M73" s="18">
-        <f>$D$30*(1+$D$33)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N73" s="18">
-        <f>$D$30*(1+$D$33)^(10-1)</f>
-        <v/>
-      </c>
+      <c r="B73" s="4" t="n"/>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="n"/>
+      <c r="J73" s="4" t="n"/>
+      <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Capacity Price</t>
+          <t>Power Price</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr</t>
+          <t>$/MWh</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -4273,165 +4220,165 @@
         </is>
       </c>
       <c r="E74" s="18">
-        <f>$D$31*(1+$D$33)^(1-1)</f>
+        <f>$D$30*(1+$D$33)^(1-1)</f>
         <v/>
       </c>
       <c r="F74" s="18">
-        <f>$D$31*(1+$D$33)^(2-1)</f>
+        <f>$D$30*(1+$D$33)^(2-1)</f>
         <v/>
       </c>
       <c r="G74" s="18">
-        <f>$D$31*(1+$D$33)^(3-1)</f>
+        <f>$D$30*(1+$D$33)^(3-1)</f>
         <v/>
       </c>
       <c r="H74" s="18">
-        <f>$D$31*(1+$D$33)^(4-1)</f>
+        <f>$D$30*(1+$D$33)^(4-1)</f>
         <v/>
       </c>
       <c r="I74" s="18">
-        <f>$D$31*(1+$D$33)^(5-1)</f>
+        <f>$D$30*(1+$D$33)^(5-1)</f>
         <v/>
       </c>
       <c r="J74" s="18">
-        <f>$D$31*(1+$D$33)^(6-1)</f>
+        <f>$D$30*(1+$D$33)^(6-1)</f>
         <v/>
       </c>
       <c r="K74" s="18">
-        <f>$D$31*(1+$D$33)^(7-1)</f>
+        <f>$D$30*(1+$D$33)^(7-1)</f>
         <v/>
       </c>
       <c r="L74" s="18">
-        <f>$D$31*(1+$D$33)^(8-1)</f>
+        <f>$D$30*(1+$D$33)^(8-1)</f>
         <v/>
       </c>
       <c r="M74" s="18">
-        <f>$D$31*(1+$D$33)^(9-1)</f>
+        <f>$D$30*(1+$D$33)^(9-1)</f>
         <v/>
       </c>
       <c r="N74" s="18">
-        <f>$D$31*(1+$D$33)^(10-1)</f>
+        <f>$D$30*(1+$D$33)^(10-1)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
+          <t>Capacity Price</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>$/kW-yr</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Escalated</t>
+        </is>
+      </c>
+      <c r="E75" s="18">
+        <f>$D$31*(1+$D$33)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F75" s="18">
+        <f>$D$31*(1+$D$33)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G75" s="18">
+        <f>$D$31*(1+$D$33)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H75" s="18">
+        <f>$D$31*(1+$D$33)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I75" s="18">
+        <f>$D$31*(1+$D$33)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J75" s="18">
+        <f>$D$31*(1+$D$33)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="K75" s="18">
+        <f>$D$31*(1+$D$33)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="L75" s="18">
+        <f>$D$31*(1+$D$33)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="M75" s="18">
+        <f>$D$31*(1+$D$33)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="N75" s="18">
+        <f>$D$31*(1+$D$33)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
           <t>Gas Price</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>$/mmBtu</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E75" s="19">
+      <c r="E76" s="19">
         <f>$D$32*(1+$D$33)^(1-1)</f>
         <v/>
       </c>
-      <c r="F75" s="19">
+      <c r="F76" s="19">
         <f>$D$32*(1+$D$33)^(2-1)</f>
         <v/>
       </c>
-      <c r="G75" s="19">
+      <c r="G76" s="19">
         <f>$D$32*(1+$D$33)^(3-1)</f>
         <v/>
       </c>
-      <c r="H75" s="19">
+      <c r="H76" s="19">
         <f>$D$32*(1+$D$33)^(4-1)</f>
         <v/>
       </c>
-      <c r="I75" s="19">
+      <c r="I76" s="19">
         <f>$D$32*(1+$D$33)^(5-1)</f>
         <v/>
       </c>
-      <c r="J75" s="19">
+      <c r="J76" s="19">
         <f>$D$32*(1+$D$33)^(6-1)</f>
         <v/>
       </c>
-      <c r="K75" s="19">
+      <c r="K76" s="19">
         <f>$D$32*(1+$D$33)^(7-1)</f>
         <v/>
       </c>
-      <c r="L75" s="19">
+      <c r="L76" s="19">
         <f>$D$32*(1+$D$33)^(8-1)</f>
         <v/>
       </c>
-      <c r="M75" s="19">
+      <c r="M76" s="19">
         <f>$D$32*(1+$D$33)^(9-1)</f>
         <v/>
       </c>
-      <c r="N75" s="19">
+      <c r="N76" s="19">
         <f>$D$32*(1+$D$33)^(10-1)</f>
         <v/>
       </c>
     </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Energy Revenue</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>Generation × Power Price / 1M</t>
-        </is>
-      </c>
-      <c r="E77" s="18">
-        <f>$D$56*E62/1000000</f>
-        <v/>
-      </c>
-      <c r="F77" s="18">
-        <f>$D$56*F62/1000000</f>
-        <v/>
-      </c>
-      <c r="G77" s="18">
-        <f>$D$56*G62/1000000</f>
-        <v/>
-      </c>
-      <c r="H77" s="18">
-        <f>$D$56*H62/1000000</f>
-        <v/>
-      </c>
-      <c r="I77" s="18">
-        <f>$D$56*I62/1000000</f>
-        <v/>
-      </c>
-      <c r="J77" s="18">
-        <f>$D$56*J62/1000000</f>
-        <v/>
-      </c>
-      <c r="K77" s="18">
-        <f>$D$56*K62/1000000</f>
-        <v/>
-      </c>
-      <c r="L77" s="18">
-        <f>$D$56*L62/1000000</f>
-        <v/>
-      </c>
-      <c r="M77" s="18">
-        <f>$D$56*M62/1000000</f>
-        <v/>
-      </c>
-      <c r="N77" s="18">
-        <f>$D$56*N62/1000000</f>
-        <v/>
-      </c>
-    </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Capacity Revenue</t>
+          <t>Energy Revenue</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -4441,173 +4388,110 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>UCAP × Cap Price × 1000 / 1M</t>
-        </is>
-      </c>
-      <c r="E78" s="18">
-        <f>$D$55*E63*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="F78" s="18">
-        <f>$D$55*F63*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="G78" s="18">
-        <f>$D$55*G63*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="H78" s="18">
-        <f>$D$55*H63*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="I78" s="18">
-        <f>$D$55*I63*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="J78" s="18">
-        <f>$D$55*J63*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="K78" s="18">
-        <f>$D$55*K63*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="L78" s="18">
-        <f>$D$55*L63*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="M78" s="18">
-        <f>$D$55*M63*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="N78" s="18">
-        <f>$D$55*N63*1000/1000000</f>
-        <v/>
-      </c>
+          <t>Generation × Power Price / 1M</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr"/>
+      <c r="F78" s="18" t="inlineStr"/>
+      <c r="G78" s="18" t="inlineStr"/>
+      <c r="H78" s="18" t="inlineStr"/>
+      <c r="I78" s="18" t="inlineStr"/>
+      <c r="J78" s="18" t="inlineStr"/>
+      <c r="K78" s="18" t="inlineStr"/>
+      <c r="L78" s="18" t="inlineStr"/>
+      <c r="M78" s="18" t="inlineStr"/>
+      <c r="N78" s="18" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
+          <t>Capacity Revenue</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>UCAP × Cap Price × 1000 / 1M</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr"/>
+      <c r="F79" s="18" t="inlineStr"/>
+      <c r="G79" s="18" t="inlineStr"/>
+      <c r="H79" s="18" t="inlineStr"/>
+      <c r="I79" s="18" t="inlineStr"/>
+      <c r="J79" s="18" t="inlineStr"/>
+      <c r="K79" s="18" t="inlineStr"/>
+      <c r="L79" s="18" t="inlineStr"/>
+      <c r="M79" s="18" t="inlineStr"/>
+      <c r="N79" s="18" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr"/>
-      <c r="E79" s="20">
-        <f>E66+E67</f>
-        <v/>
-      </c>
-      <c r="F79" s="20">
-        <f>F66+F67</f>
-        <v/>
-      </c>
-      <c r="G79" s="20">
-        <f>G66+G67</f>
-        <v/>
-      </c>
-      <c r="H79" s="20">
-        <f>H66+H67</f>
-        <v/>
-      </c>
-      <c r="I79" s="20">
-        <f>I66+I67</f>
-        <v/>
-      </c>
-      <c r="J79" s="20">
-        <f>J66+J67</f>
-        <v/>
-      </c>
-      <c r="K79" s="20">
-        <f>K66+K67</f>
-        <v/>
-      </c>
-      <c r="L79" s="20">
-        <f>L66+L67</f>
-        <v/>
-      </c>
-      <c r="M79" s="20">
-        <f>M66+M67</f>
-        <v/>
-      </c>
-      <c r="N79" s="20">
-        <f>N66+N67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr"/>
+      <c r="E80" s="20" t="inlineStr"/>
+      <c r="F80" s="20" t="inlineStr"/>
+      <c r="G80" s="20" t="inlineStr"/>
+      <c r="H80" s="20" t="inlineStr"/>
+      <c r="I80" s="20" t="inlineStr"/>
+      <c r="J80" s="20" t="inlineStr"/>
+      <c r="K80" s="20" t="inlineStr"/>
+      <c r="L80" s="20" t="inlineStr"/>
+      <c r="M80" s="20" t="inlineStr"/>
+      <c r="N80" s="20" t="inlineStr"/>
+    </row>
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>Fuel Cost</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>Gen × HR × Gas / 1B</t>
         </is>
       </c>
-      <c r="E81" s="18">
-        <f>$D$56*$D$24*E64/1E9</f>
-        <v/>
-      </c>
-      <c r="F81" s="18">
-        <f>$D$56*$D$24*F64/1E9</f>
-        <v/>
-      </c>
-      <c r="G81" s="18">
-        <f>$D$56*$D$24*G64/1E9</f>
-        <v/>
-      </c>
-      <c r="H81" s="18">
-        <f>$D$56*$D$24*H64/1E9</f>
-        <v/>
-      </c>
-      <c r="I81" s="18">
-        <f>$D$56*$D$24*I64/1E9</f>
-        <v/>
-      </c>
-      <c r="J81" s="18">
-        <f>$D$56*$D$24*J64/1E9</f>
-        <v/>
-      </c>
-      <c r="K81" s="18">
-        <f>$D$56*$D$24*K64/1E9</f>
-        <v/>
-      </c>
-      <c r="L81" s="18">
-        <f>$D$56*$D$24*L64/1E9</f>
-        <v/>
-      </c>
-      <c r="M81" s="18">
-        <f>$D$56*$D$24*M64/1E9</f>
-        <v/>
-      </c>
-      <c r="N81" s="18">
-        <f>$D$56*$D$24*N64/1E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="34" t="inlineStr">
+      <c r="E82" s="18" t="inlineStr"/>
+      <c r="F82" s="18" t="inlineStr"/>
+      <c r="G82" s="18" t="inlineStr"/>
+      <c r="H82" s="18" t="inlineStr"/>
+      <c r="I82" s="18" t="inlineStr"/>
+      <c r="J82" s="18" t="inlineStr"/>
+      <c r="K82" s="18" t="inlineStr"/>
+      <c r="L82" s="18" t="inlineStr"/>
+      <c r="M82" s="18" t="inlineStr"/>
+      <c r="N82" s="18" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="34" t="inlineStr">
         <is>
           <t>Spark Spread</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>$/MWh</t>
         </is>
       </c>
-      <c r="C82" s="55" t="inlineStr">
+      <c r="C83" s="55" t="inlineStr">
         <is>
           <t>[WHAT] Spark Spread = Power Price - (Plant HR × Gas / 1000)
 [WHY] Gross margin per MWh after fuel. Core driver of thermal profitability.
@@ -4625,108 +4509,51 @@
 [UNITS] $/MWh - (Btu/kWh × $/MMBtu / 1000) = $/MWh ✓</t>
         </is>
       </c>
-      <c r="E82" s="56">
+      <c r="E83" s="56">
         <f>E72-($D$34/1000)*E74</f>
         <v/>
       </c>
-      <c r="F82" s="56">
+      <c r="F83" s="56">
         <f>F72-($D$34/1000)*F74</f>
         <v/>
       </c>
-      <c r="G82" s="56">
+      <c r="G83" s="56">
         <f>G72-($D$34/1000)*G74</f>
         <v/>
       </c>
-      <c r="H82" s="56">
+      <c r="H83" s="56">
         <f>H72-($D$34/1000)*H74</f>
         <v/>
       </c>
-      <c r="I82" s="56">
+      <c r="I83" s="56">
         <f>I72-($D$34/1000)*I74</f>
         <v/>
       </c>
-      <c r="J82" s="56">
+      <c r="J83" s="56">
         <f>J72-($D$34/1000)*J74</f>
         <v/>
       </c>
-      <c r="K82" s="56">
+      <c r="K83" s="56">
         <f>K72-($D$34/1000)*K74</f>
         <v/>
       </c>
-      <c r="L82" s="56">
+      <c r="L83" s="56">
         <f>L72-($D$34/1000)*L74</f>
         <v/>
       </c>
-      <c r="M82" s="56">
+      <c r="M83" s="56">
         <f>M72-($D$34/1000)*M74</f>
         <v/>
       </c>
-      <c r="N82" s="56">
+      <c r="N83" s="56">
         <f>N72-($D$34/1000)*N74</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>VOM</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>Generation × VOM rate / 1M</t>
-        </is>
-      </c>
-      <c r="E83" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="F83" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="G83" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="H83" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="I83" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="J83" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="K83" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="L83" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="M83" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="N83" s="18">
-        <f>$D$56*$D$36/1000000</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>FOM</t>
+          <t>VOM</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -4736,239 +4563,209 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Capacity × FOM × esc × 1000 / 1M</t>
+          <t>Generation × VOM rate / 1M</t>
         </is>
       </c>
       <c r="E84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(1-1)*1000/1000000</f>
+        <f>$D$56*$D$36/1000000</f>
         <v/>
       </c>
       <c r="F84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(2-1)*1000/1000000</f>
+        <f>$D$56*$D$36/1000000</f>
         <v/>
       </c>
       <c r="G84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(3-1)*1000/1000000</f>
+        <f>$D$56*$D$36/1000000</f>
         <v/>
       </c>
       <c r="H84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(4-1)*1000/1000000</f>
+        <f>$D$56*$D$36/1000000</f>
         <v/>
       </c>
       <c r="I84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(5-1)*1000/1000000</f>
+        <f>$D$56*$D$36/1000000</f>
         <v/>
       </c>
       <c r="J84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(6-1)*1000/1000000</f>
+        <f>$D$56*$D$36/1000000</f>
         <v/>
       </c>
       <c r="K84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(7-1)*1000/1000000</f>
+        <f>$D$56*$D$36/1000000</f>
         <v/>
       </c>
       <c r="L84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(8-1)*1000/1000000</f>
+        <f>$D$56*$D$36/1000000</f>
         <v/>
       </c>
       <c r="M84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(9-1)*1000/1000000</f>
+        <f>$D$56*$D$36/1000000</f>
         <v/>
       </c>
       <c r="N84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(10-1)*1000/1000000</f>
+        <f>$D$56*$D$36/1000000</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
+          <t>FOM</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Capacity × FOM × esc × 1000 / 1M</t>
+        </is>
+      </c>
+      <c r="E85" s="18">
+        <f>$D$23*$D$37*(1+$D$33)^(1-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="F85" s="18">
+        <f>$D$23*$D$37*(1+$D$33)^(2-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="G85" s="18">
+        <f>$D$23*$D$37*(1+$D$33)^(3-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="H85" s="18">
+        <f>$D$23*$D$37*(1+$D$33)^(4-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="I85" s="18">
+        <f>$D$23*$D$37*(1+$D$33)^(5-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="J85" s="18">
+        <f>$D$23*$D$37*(1+$D$33)^(6-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="K85" s="18">
+        <f>$D$23*$D$37*(1+$D$33)^(7-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="L85" s="18">
+        <f>$D$23*$D$37*(1+$D$33)^(8-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="M85" s="18">
+        <f>$D$23*$D$37*(1+$D$33)^(9-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="N85" s="18">
+        <f>$D$23*$D$37*(1+$D$33)^(10-1)*1000/1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
           <t>Total Operating Costs</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr"/>
-      <c r="E85" s="18">
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr"/>
+      <c r="E86" s="18">
         <f>E70+E71+E72</f>
         <v/>
       </c>
-      <c r="F85" s="18">
+      <c r="F86" s="18">
         <f>F70+F71+F72</f>
         <v/>
       </c>
-      <c r="G85" s="18">
+      <c r="G86" s="18">
         <f>G70+G71+G72</f>
         <v/>
       </c>
-      <c r="H85" s="18">
+      <c r="H86" s="18">
         <f>H70+H71+H72</f>
         <v/>
       </c>
-      <c r="I85" s="18">
+      <c r="I86" s="18">
         <f>I70+I71+I72</f>
         <v/>
       </c>
-      <c r="J85" s="18">
+      <c r="J86" s="18">
         <f>J70+J71+J72</f>
         <v/>
       </c>
-      <c r="K85" s="18">
+      <c r="K86" s="18">
         <f>K70+K71+K72</f>
         <v/>
       </c>
-      <c r="L85" s="18">
+      <c r="L86" s="18">
         <f>L70+L71+L72</f>
         <v/>
       </c>
-      <c r="M85" s="18">
+      <c r="M86" s="18">
         <f>M70+M71+M72</f>
         <v/>
       </c>
-      <c r="N85" s="18">
+      <c r="N86" s="18">
         <f>N70+N71+N72</f>
         <v/>
       </c>
     </row>
-    <row r="86"/>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+    <row r="87"/>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr"/>
-      <c r="E87" s="7">
-        <f>E68-E73</f>
-        <v/>
-      </c>
-      <c r="F87" s="7">
-        <f>F68-F73</f>
-        <v/>
-      </c>
-      <c r="G87" s="7">
-        <f>G68-G73</f>
-        <v/>
-      </c>
-      <c r="H87" s="7">
-        <f>H68-H73</f>
-        <v/>
-      </c>
-      <c r="I87" s="7">
-        <f>I68-I73</f>
-        <v/>
-      </c>
-      <c r="J87" s="7">
-        <f>J68-J73</f>
-        <v/>
-      </c>
-      <c r="K87" s="7">
-        <f>K68-K73</f>
-        <v/>
-      </c>
-      <c r="L87" s="7">
-        <f>L68-L73</f>
-        <v/>
-      </c>
-      <c r="M87" s="7">
-        <f>M68-M73</f>
-        <v/>
-      </c>
-      <c r="N87" s="7">
-        <f>N68-N73</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88"/>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr"/>
+      <c r="E88" s="7" t="inlineStr"/>
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr"/>
+      <c r="K88" s="7" t="inlineStr"/>
+      <c r="L88" s="7" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+      <c r="N88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>CASH FLOW</t>
         </is>
       </c>
-      <c r="B89" s="4" t="n"/>
-      <c r="C89" s="4" t="n"/>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n"/>
-      <c r="F89" s="4" t="n"/>
-      <c r="G89" s="4" t="n"/>
-      <c r="H89" s="4" t="n"/>
-      <c r="I89" s="4" t="n"/>
-      <c r="J89" s="4" t="n"/>
-      <c r="K89" s="4" t="n"/>
-      <c r="L89" s="4" t="n"/>
-      <c r="M89" s="4" t="n"/>
-      <c r="N89" s="4" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA - Depreciation</t>
-        </is>
-      </c>
-      <c r="E90" s="18">
-        <f>E75-$D$58</f>
-        <v/>
-      </c>
-      <c r="F90" s="18">
-        <f>F75-$D$58</f>
-        <v/>
-      </c>
-      <c r="G90" s="18">
-        <f>G75-$D$58</f>
-        <v/>
-      </c>
-      <c r="H90" s="18">
-        <f>H75-$D$58</f>
-        <v/>
-      </c>
-      <c r="I90" s="18">
-        <f>I75-$D$58</f>
-        <v/>
-      </c>
-      <c r="J90" s="18">
-        <f>J75-$D$58</f>
-        <v/>
-      </c>
-      <c r="K90" s="18">
-        <f>K75-$D$58</f>
-        <v/>
-      </c>
-      <c r="L90" s="18">
-        <f>L75-$D$58</f>
-        <v/>
-      </c>
-      <c r="M90" s="18">
-        <f>M75-$D$58</f>
-        <v/>
-      </c>
-      <c r="N90" s="18">
-        <f>N75-$D$58</f>
-        <v/>
-      </c>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="n"/>
+      <c r="E90" s="4" t="n"/>
+      <c r="F90" s="4" t="n"/>
+      <c r="G90" s="4" t="n"/>
+      <c r="H90" s="4" t="n"/>
+      <c r="I90" s="4" t="n"/>
+      <c r="J90" s="4" t="n"/>
+      <c r="K90" s="4" t="n"/>
+      <c r="L90" s="4" t="n"/>
+      <c r="M90" s="4" t="n"/>
+      <c r="N90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>EBIT</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -4978,54 +4775,24 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, EBIT) × Tax Rate</t>
-        </is>
-      </c>
-      <c r="E91" s="18">
-        <f>MAX(0,E78)*$D$50</f>
-        <v/>
-      </c>
-      <c r="F91" s="18">
-        <f>MAX(0,F78)*$D$50</f>
-        <v/>
-      </c>
-      <c r="G91" s="18">
-        <f>MAX(0,G78)*$D$50</f>
-        <v/>
-      </c>
-      <c r="H91" s="18">
-        <f>MAX(0,H78)*$D$50</f>
-        <v/>
-      </c>
-      <c r="I91" s="18">
-        <f>MAX(0,I78)*$D$50</f>
-        <v/>
-      </c>
-      <c r="J91" s="18">
-        <f>MAX(0,J78)*$D$50</f>
-        <v/>
-      </c>
-      <c r="K91" s="18">
-        <f>MAX(0,K78)*$D$50</f>
-        <v/>
-      </c>
-      <c r="L91" s="18">
-        <f>MAX(0,L78)*$D$50</f>
-        <v/>
-      </c>
-      <c r="M91" s="18">
-        <f>MAX(0,M78)*$D$50</f>
-        <v/>
-      </c>
-      <c r="N91" s="18">
-        <f>MAX(0,N78)*$D$50</f>
-        <v/>
-      </c>
+          <t>EBITDA - Depreciation</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="inlineStr"/>
+      <c r="F91" s="18" t="inlineStr"/>
+      <c r="G91" s="18" t="inlineStr"/>
+      <c r="H91" s="18" t="inlineStr"/>
+      <c r="I91" s="18" t="inlineStr"/>
+      <c r="J91" s="18" t="inlineStr"/>
+      <c r="K91" s="18" t="inlineStr"/>
+      <c r="L91" s="18" t="inlineStr"/>
+      <c r="M91" s="18" t="inlineStr"/>
+      <c r="N91" s="18" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Major Maintenance</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -5035,185 +4802,129 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>HGP in specified year</t>
-        </is>
-      </c>
-      <c r="E92" s="21">
-        <f>IF(1=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="F92" s="21">
-        <f>IF(2=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="G92" s="21">
-        <f>IF(3=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="H92" s="21">
-        <f>IF(4=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="I92" s="21">
-        <f>IF(5=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="J92" s="21">
-        <f>IF(6=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="K92" s="21">
-        <f>IF(7=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="L92" s="21">
-        <f>IF(8=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="M92" s="21">
-        <f>IF(9=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="N92" s="21">
-        <f>IF(10=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
+          <t>MAX(0, EBIT) × Tax Rate</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="inlineStr"/>
+      <c r="F92" s="18" t="inlineStr"/>
+      <c r="G92" s="18" t="inlineStr"/>
+      <c r="H92" s="18" t="inlineStr"/>
+      <c r="I92" s="18" t="inlineStr"/>
+      <c r="J92" s="18" t="inlineStr"/>
+      <c r="K92" s="18" t="inlineStr"/>
+      <c r="L92" s="18" t="inlineStr"/>
+      <c r="M92" s="18" t="inlineStr"/>
+      <c r="N92" s="18" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
+          <t>Major Maintenance</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>HGP in specified year</t>
+        </is>
+      </c>
+      <c r="E93" s="21">
+        <f>IF(1=$D$38,$D$39,0)</f>
+        <v/>
+      </c>
+      <c r="F93" s="21">
+        <f>IF(2=$D$38,$D$39,0)</f>
+        <v/>
+      </c>
+      <c r="G93" s="21">
+        <f>IF(3=$D$38,$D$39,0)</f>
+        <v/>
+      </c>
+      <c r="H93" s="21">
+        <f>IF(4=$D$38,$D$39,0)</f>
+        <v/>
+      </c>
+      <c r="I93" s="21">
+        <f>IF(5=$D$38,$D$39,0)</f>
+        <v/>
+      </c>
+      <c r="J93" s="21">
+        <f>IF(6=$D$38,$D$39,0)</f>
+        <v/>
+      </c>
+      <c r="K93" s="21">
+        <f>IF(7=$D$38,$D$39,0)</f>
+        <v/>
+      </c>
+      <c r="L93" s="21">
+        <f>IF(8=$D$38,$D$39,0)</f>
+        <v/>
+      </c>
+      <c r="M93" s="21">
+        <f>IF(9=$D$38,$D$39,0)</f>
+        <v/>
+      </c>
+      <c r="N93" s="21">
+        <f>IF(10=$D$38,$D$39,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
           <t>CFADS</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>EBITDA - Taxes - Maint</t>
         </is>
       </c>
-      <c r="E93" s="7">
-        <f>E75-E79-E80</f>
-        <v/>
-      </c>
-      <c r="F93" s="7">
-        <f>F75-F79-F80</f>
-        <v/>
-      </c>
-      <c r="G93" s="7">
-        <f>G75-G79-G80</f>
-        <v/>
-      </c>
-      <c r="H93" s="7">
-        <f>H75-H79-H80</f>
-        <v/>
-      </c>
-      <c r="I93" s="7">
-        <f>I75-I79-I80</f>
-        <v/>
-      </c>
-      <c r="J93" s="7">
-        <f>J75-J79-J80</f>
-        <v/>
-      </c>
-      <c r="K93" s="7">
-        <f>K75-K79-K80</f>
-        <v/>
-      </c>
-      <c r="L93" s="7">
-        <f>L75-L79-L80</f>
-        <v/>
-      </c>
-      <c r="M93" s="7">
-        <f>M75-M79-M80</f>
-        <v/>
-      </c>
-      <c r="N93" s="7">
-        <f>N75-N79-N80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94"/>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr"/>
+      <c r="F94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr"/>
+      <c r="H94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr"/>
+      <c r="J94" s="7" t="inlineStr"/>
+      <c r="K94" s="7" t="inlineStr"/>
+      <c r="L94" s="7" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+      <c r="N94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>DEBT SCHEDULE (50% Cash Sweep)</t>
         </is>
       </c>
-      <c r="B95" s="4" t="n"/>
-      <c r="C95" s="4" t="n"/>
-      <c r="D95" s="4" t="n"/>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="4" t="n"/>
-      <c r="G95" s="4" t="n"/>
-      <c r="H95" s="4" t="n"/>
-      <c r="I95" s="4" t="n"/>
-      <c r="J95" s="4" t="n"/>
-      <c r="K95" s="4" t="n"/>
-      <c r="L95" s="4" t="n"/>
-      <c r="M95" s="4" t="n"/>
-      <c r="N95" s="4" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Beginning Balance</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr"/>
-      <c r="E96" s="18">
-        <f>$D$57</f>
-        <v/>
-      </c>
-      <c r="F96" s="18">
-        <f>E91</f>
-        <v/>
-      </c>
-      <c r="G96" s="18">
-        <f>F91</f>
-        <v/>
-      </c>
-      <c r="H96" s="18">
-        <f>G91</f>
-        <v/>
-      </c>
-      <c r="I96" s="18">
-        <f>H91</f>
-        <v/>
-      </c>
-      <c r="J96" s="18">
-        <f>I91</f>
-        <v/>
-      </c>
-      <c r="K96" s="18">
-        <f>J91</f>
-        <v/>
-      </c>
-      <c r="L96" s="18">
-        <f>K91</f>
-        <v/>
-      </c>
-      <c r="M96" s="18">
-        <f>L91</f>
-        <v/>
-      </c>
-      <c r="N96" s="18">
-        <f>M91</f>
-        <v/>
-      </c>
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="n"/>
+      <c r="H96" s="4" t="n"/>
+      <c r="I96" s="4" t="n"/>
+      <c r="J96" s="4" t="n"/>
+      <c r="K96" s="4" t="n"/>
+      <c r="L96" s="4" t="n"/>
+      <c r="M96" s="4" t="n"/>
+      <c r="N96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Beginning Balance</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -5221,56 +4932,52 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>Beg Bal × Int Rate</t>
-        </is>
-      </c>
+      <c r="C97" s="6" t="inlineStr"/>
       <c r="E97" s="18">
-        <f>E84*$D$43</f>
+        <f>$D$57</f>
         <v/>
       </c>
       <c r="F97" s="18">
-        <f>F84*$D$43</f>
+        <f>E91</f>
         <v/>
       </c>
       <c r="G97" s="18">
-        <f>G84*$D$43</f>
+        <f>F91</f>
         <v/>
       </c>
       <c r="H97" s="18">
-        <f>H84*$D$43</f>
+        <f>G91</f>
         <v/>
       </c>
       <c r="I97" s="18">
-        <f>I84*$D$43</f>
+        <f>H91</f>
         <v/>
       </c>
       <c r="J97" s="18">
-        <f>J84*$D$43</f>
+        <f>I91</f>
         <v/>
       </c>
       <c r="K97" s="18">
-        <f>K84*$D$43</f>
+        <f>J91</f>
         <v/>
       </c>
       <c r="L97" s="18">
-        <f>L84*$D$43</f>
+        <f>K91</f>
         <v/>
       </c>
       <c r="M97" s="18">
-        <f>M84*$D$43</f>
+        <f>L91</f>
         <v/>
       </c>
       <c r="N97" s="18">
-        <f>N84*$D$43</f>
+        <f>M91</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Scheduled Principal</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -5280,54 +4987,24 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>MIN(Sched, Beg Bal)</t>
-        </is>
-      </c>
-      <c r="E98" s="18">
-        <f>MIN($D$59,E84)</f>
-        <v/>
-      </c>
-      <c r="F98" s="18">
-        <f>MIN($D$59,F84)</f>
-        <v/>
-      </c>
-      <c r="G98" s="18">
-        <f>MIN($D$59,G84)</f>
-        <v/>
-      </c>
-      <c r="H98" s="18">
-        <f>MIN($D$59,H84)</f>
-        <v/>
-      </c>
-      <c r="I98" s="18">
-        <f>MIN($D$59,I84)</f>
-        <v/>
-      </c>
-      <c r="J98" s="18">
-        <f>MIN($D$59,J84)</f>
-        <v/>
-      </c>
-      <c r="K98" s="18">
-        <f>MIN($D$59,K84)</f>
-        <v/>
-      </c>
-      <c r="L98" s="18">
-        <f>MIN($D$59,L84)</f>
-        <v/>
-      </c>
-      <c r="M98" s="18">
-        <f>MIN($D$59,M84)</f>
-        <v/>
-      </c>
-      <c r="N98" s="18">
-        <f>MIN($D$59,N84)</f>
-        <v/>
-      </c>
+          <t>Beg Bal × Int Rate</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr"/>
+      <c r="F98" s="18" t="inlineStr"/>
+      <c r="G98" s="18" t="inlineStr"/>
+      <c r="H98" s="18" t="inlineStr"/>
+      <c r="I98" s="18" t="inlineStr"/>
+      <c r="J98" s="18" t="inlineStr"/>
+      <c r="K98" s="18" t="inlineStr"/>
+      <c r="L98" s="18" t="inlineStr"/>
+      <c r="M98" s="18" t="inlineStr"/>
+      <c r="N98" s="18" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Debt Service (Pre-Sweep)</t>
+          <t>Scheduled Principal</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -5337,54 +5014,24 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Interest + Sched Prin</t>
-        </is>
-      </c>
-      <c r="E99" s="18">
-        <f>E85+E86</f>
-        <v/>
-      </c>
-      <c r="F99" s="18">
-        <f>F85+F86</f>
-        <v/>
-      </c>
-      <c r="G99" s="18">
-        <f>G85+G86</f>
-        <v/>
-      </c>
-      <c r="H99" s="18">
-        <f>H85+H86</f>
-        <v/>
-      </c>
-      <c r="I99" s="18">
-        <f>I85+I86</f>
-        <v/>
-      </c>
-      <c r="J99" s="18">
-        <f>J85+J86</f>
-        <v/>
-      </c>
-      <c r="K99" s="18">
-        <f>K85+K86</f>
-        <v/>
-      </c>
-      <c r="L99" s="18">
-        <f>L85+L86</f>
-        <v/>
-      </c>
-      <c r="M99" s="18">
-        <f>M85+M86</f>
-        <v/>
-      </c>
-      <c r="N99" s="18">
-        <f>N85+N86</f>
-        <v/>
-      </c>
+          <t>MIN(Sched, Beg Bal)</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="inlineStr"/>
+      <c r="F99" s="18" t="inlineStr"/>
+      <c r="G99" s="18" t="inlineStr"/>
+      <c r="H99" s="18" t="inlineStr"/>
+      <c r="I99" s="18" t="inlineStr"/>
+      <c r="J99" s="18" t="inlineStr"/>
+      <c r="K99" s="18" t="inlineStr"/>
+      <c r="L99" s="18" t="inlineStr"/>
+      <c r="M99" s="18" t="inlineStr"/>
+      <c r="N99" s="18" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Excess Cash</t>
+          <t>Debt Service (Pre-Sweep)</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -5394,54 +5041,54 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>CFADS - DS - DSRA Funding</t>
+          <t>Interest + Sched Prin</t>
         </is>
       </c>
       <c r="E100" s="18">
-        <f>MAX(0,E81-E87-E97)</f>
+        <f>E85+E86</f>
         <v/>
       </c>
       <c r="F100" s="18">
-        <f>MAX(0,F81-F87-F97)</f>
+        <f>F85+F86</f>
         <v/>
       </c>
       <c r="G100" s="18">
-        <f>MAX(0,G81-G87-G97)</f>
+        <f>G85+G86</f>
         <v/>
       </c>
       <c r="H100" s="18">
-        <f>MAX(0,H81-H87-H97)</f>
+        <f>H85+H86</f>
         <v/>
       </c>
       <c r="I100" s="18">
-        <f>MAX(0,I81-I87-I97)</f>
+        <f>I85+I86</f>
         <v/>
       </c>
       <c r="J100" s="18">
-        <f>MAX(0,J81-J87-J97)</f>
+        <f>J85+J86</f>
         <v/>
       </c>
       <c r="K100" s="18">
-        <f>MAX(0,K81-K87-K97)</f>
+        <f>K85+K86</f>
         <v/>
       </c>
       <c r="L100" s="18">
-        <f>MAX(0,L81-L87-L97)</f>
+        <f>L85+L86</f>
         <v/>
       </c>
       <c r="M100" s="18">
-        <f>MAX(0,M81-M87-M97)</f>
+        <f>M85+M86</f>
         <v/>
       </c>
       <c r="N100" s="18">
-        <f>MAX(0,N81-N87-N97)</f>
+        <f>N85+N86</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep</t>
+          <t>Excess Cash</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -5451,54 +5098,54 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>MIN(Excess×50%, Beg-Sched)</t>
-        </is>
-      </c>
-      <c r="E101" s="21">
-        <f>MIN(MAX(0,E88)*$D$46,MAX(0,E84-E86))</f>
-        <v/>
-      </c>
-      <c r="F101" s="21">
-        <f>MIN(MAX(0,F88)*$D$46,MAX(0,F84-F86))</f>
-        <v/>
-      </c>
-      <c r="G101" s="21">
-        <f>MIN(MAX(0,G88)*$D$46,MAX(0,G84-G86))</f>
-        <v/>
-      </c>
-      <c r="H101" s="21">
-        <f>MIN(MAX(0,H88)*$D$46,MAX(0,H84-H86))</f>
-        <v/>
-      </c>
-      <c r="I101" s="21">
-        <f>MIN(MAX(0,I88)*$D$46,MAX(0,I84-I86))</f>
-        <v/>
-      </c>
-      <c r="J101" s="21">
-        <f>MIN(MAX(0,J88)*$D$46,MAX(0,J84-J86))</f>
-        <v/>
-      </c>
-      <c r="K101" s="21">
-        <f>MIN(MAX(0,K88)*$D$46,MAX(0,K84-K86))</f>
-        <v/>
-      </c>
-      <c r="L101" s="21">
-        <f>MIN(MAX(0,L88)*$D$46,MAX(0,L84-L86))</f>
-        <v/>
-      </c>
-      <c r="M101" s="21">
-        <f>MIN(MAX(0,M88)*$D$46,MAX(0,M84-M86))</f>
-        <v/>
-      </c>
-      <c r="N101" s="21">
-        <f>MIN(MAX(0,N88)*$D$46,MAX(0,N84-N86))</f>
+          <t>CFADS - DS - DSRA Funding</t>
+        </is>
+      </c>
+      <c r="E101" s="18">
+        <f>MAX(0,E81-E87-E97)</f>
+        <v/>
+      </c>
+      <c r="F101" s="18">
+        <f>MAX(0,F81-F87-F97)</f>
+        <v/>
+      </c>
+      <c r="G101" s="18">
+        <f>MAX(0,G81-G87-G97)</f>
+        <v/>
+      </c>
+      <c r="H101" s="18">
+        <f>MAX(0,H81-H87-H97)</f>
+        <v/>
+      </c>
+      <c r="I101" s="18">
+        <f>MAX(0,I81-I87-I97)</f>
+        <v/>
+      </c>
+      <c r="J101" s="18">
+        <f>MAX(0,J81-J87-J97)</f>
+        <v/>
+      </c>
+      <c r="K101" s="18">
+        <f>MAX(0,K81-K87-K97)</f>
+        <v/>
+      </c>
+      <c r="L101" s="18">
+        <f>MAX(0,L81-L87-L97)</f>
+        <v/>
+      </c>
+      <c r="M101" s="18">
+        <f>MAX(0,M81-M87-M97)</f>
+        <v/>
+      </c>
+      <c r="N101" s="18">
+        <f>MAX(0,N81-N87-N97)</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Total Principal</t>
+          <t>Cash Sweep</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
@@ -5508,54 +5155,24 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Scheduled + Sweep</t>
-        </is>
-      </c>
-      <c r="E102" s="18">
-        <f>E86+E89</f>
-        <v/>
-      </c>
-      <c r="F102" s="18">
-        <f>F86+F89</f>
-        <v/>
-      </c>
-      <c r="G102" s="18">
-        <f>G86+G89</f>
-        <v/>
-      </c>
-      <c r="H102" s="18">
-        <f>H86+H89</f>
-        <v/>
-      </c>
-      <c r="I102" s="18">
-        <f>I86+I89</f>
-        <v/>
-      </c>
-      <c r="J102" s="18">
-        <f>J86+J89</f>
-        <v/>
-      </c>
-      <c r="K102" s="18">
-        <f>K86+K89</f>
-        <v/>
-      </c>
-      <c r="L102" s="18">
-        <f>L86+L89</f>
-        <v/>
-      </c>
-      <c r="M102" s="18">
-        <f>M86+M89</f>
-        <v/>
-      </c>
-      <c r="N102" s="18">
-        <f>N86+N89</f>
-        <v/>
-      </c>
+          <t>MIN(Excess×50%, Beg-Sched)</t>
+        </is>
+      </c>
+      <c r="E102" s="21" t="inlineStr"/>
+      <c r="F102" s="21" t="inlineStr"/>
+      <c r="G102" s="21" t="inlineStr"/>
+      <c r="H102" s="21" t="inlineStr"/>
+      <c r="I102" s="21" t="inlineStr"/>
+      <c r="J102" s="21" t="inlineStr"/>
+      <c r="K102" s="21" t="inlineStr"/>
+      <c r="L102" s="21" t="inlineStr"/>
+      <c r="M102" s="21" t="inlineStr"/>
+      <c r="N102" s="21" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Ending Balance</t>
+          <t>Total Principal</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -5565,249 +5182,155 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, Beg - Total Prin)</t>
-        </is>
-      </c>
-      <c r="E103" s="18">
-        <f>MAX(0,E84-E90)</f>
-        <v/>
-      </c>
-      <c r="F103" s="18">
-        <f>MAX(0,F84-F90)</f>
-        <v/>
-      </c>
-      <c r="G103" s="18">
-        <f>MAX(0,G84-G90)</f>
-        <v/>
-      </c>
-      <c r="H103" s="18">
-        <f>MAX(0,H84-H90)</f>
-        <v/>
-      </c>
-      <c r="I103" s="18">
-        <f>MAX(0,I84-I90)</f>
-        <v/>
-      </c>
-      <c r="J103" s="18">
-        <f>MAX(0,J84-J90)</f>
-        <v/>
-      </c>
-      <c r="K103" s="18">
-        <f>MAX(0,K84-K90)</f>
-        <v/>
-      </c>
-      <c r="L103" s="18">
-        <f>MAX(0,L84-L90)</f>
-        <v/>
-      </c>
-      <c r="M103" s="18">
-        <f>MAX(0,M84-M90)</f>
-        <v/>
-      </c>
-      <c r="N103" s="18">
-        <f>MAX(0,N84-N90)</f>
-        <v/>
-      </c>
+          <t>Scheduled + Sweep</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="inlineStr"/>
+      <c r="F103" s="18" t="inlineStr"/>
+      <c r="G103" s="18" t="inlineStr"/>
+      <c r="H103" s="18" t="inlineStr"/>
+      <c r="I103" s="18" t="inlineStr"/>
+      <c r="J103" s="18" t="inlineStr"/>
+      <c r="K103" s="18" t="inlineStr"/>
+      <c r="L103" s="18" t="inlineStr"/>
+      <c r="M103" s="18" t="inlineStr"/>
+      <c r="N103" s="18" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>DSCR</t>
+          <t>Ending Balance</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="E104" s="30">
-        <f>IF(E87&gt;0,E81/E87,0)</f>
-        <v/>
-      </c>
-      <c r="F104" s="30">
-        <f>IF(F87&gt;0,F81/F87,0)</f>
-        <v/>
-      </c>
-      <c r="G104" s="30">
-        <f>IF(G87&gt;0,G81/G87,0)</f>
-        <v/>
-      </c>
-      <c r="H104" s="30">
-        <f>IF(H87&gt;0,H81/H87,0)</f>
-        <v/>
-      </c>
-      <c r="I104" s="30">
-        <f>IF(I87&gt;0,I81/I87,0)</f>
-        <v/>
-      </c>
-      <c r="J104" s="30">
-        <f>IF(J87&gt;0,J81/J87,0)</f>
-        <v/>
-      </c>
-      <c r="K104" s="30">
-        <f>IF(K87&gt;0,K81/K87,0)</f>
-        <v/>
-      </c>
-      <c r="L104" s="30">
-        <f>IF(L87&gt;0,L81/L87,0)</f>
-        <v/>
-      </c>
-      <c r="M104" s="30">
-        <f>IF(M87&gt;0,M81/M87,0)</f>
-        <v/>
-      </c>
-      <c r="N104" s="30">
-        <f>IF(N87&gt;0,N81/N87,0)</f>
-        <v/>
-      </c>
+          <t>MAX(0, Beg - Total Prin)</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr"/>
+      <c r="F104" s="18" t="inlineStr"/>
+      <c r="G104" s="18" t="inlineStr"/>
+      <c r="H104" s="18" t="inlineStr"/>
+      <c r="I104" s="18" t="inlineStr"/>
+      <c r="J104" s="18" t="inlineStr"/>
+      <c r="K104" s="18" t="inlineStr"/>
+      <c r="L104" s="18" t="inlineStr"/>
+      <c r="M104" s="18" t="inlineStr"/>
+      <c r="N104" s="18" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
+          <t>DSCR</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
+      <c r="E105" s="30" t="inlineStr"/>
+      <c r="F105" s="30" t="inlineStr"/>
+      <c r="G105" s="30" t="inlineStr"/>
+      <c r="H105" s="30" t="inlineStr"/>
+      <c r="I105" s="30" t="inlineStr"/>
+      <c r="J105" s="30" t="inlineStr"/>
+      <c r="K105" s="30" t="inlineStr"/>
+      <c r="L105" s="30" t="inlineStr"/>
+      <c r="M105" s="30" t="inlineStr"/>
+      <c r="N105" s="30" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
           <t>Scheduled DS (for DSRA)</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>Based on straight-line amort</t>
         </is>
       </c>
-      <c r="E105" s="18">
+      <c r="E106" s="18">
         <f>MAX(0,$D$57-(1-1)*$D$59)*$D$43+$D$59</f>
         <v/>
       </c>
-      <c r="F105" s="18">
+      <c r="F106" s="18">
         <f>MAX(0,$D$57-(2-1)*$D$59)*$D$43+$D$59</f>
         <v/>
       </c>
-      <c r="G105" s="18">
+      <c r="G106" s="18">
         <f>MAX(0,$D$57-(3-1)*$D$59)*$D$43+$D$59</f>
         <v/>
       </c>
-      <c r="H105" s="18">
+      <c r="H106" s="18">
         <f>MAX(0,$D$57-(4-1)*$D$59)*$D$43+$D$59</f>
         <v/>
       </c>
-      <c r="I105" s="18">
+      <c r="I106" s="18">
         <f>MAX(0,$D$57-(5-1)*$D$59)*$D$43+$D$59</f>
         <v/>
       </c>
-      <c r="J105" s="18">
+      <c r="J106" s="18">
         <f>MAX(0,$D$57-(6-1)*$D$59)*$D$43+$D$59</f>
         <v/>
       </c>
-      <c r="K105" s="18">
+      <c r="K106" s="18">
         <f>MAX(0,$D$57-(7-1)*$D$59)*$D$43+$D$59</f>
         <v/>
       </c>
-      <c r="L105" s="18">
+      <c r="L106" s="18">
         <f>MAX(0,$D$57-(8-1)*$D$59)*$D$43+$D$59</f>
         <v/>
       </c>
-      <c r="M105" s="18">
+      <c r="M106" s="18">
         <f>MAX(0,$D$57-(9-1)*$D$59)*$D$43+$D$59</f>
         <v/>
       </c>
-      <c r="N105" s="18">
+      <c r="N106" s="18">
         <f>MAX(0,$D$57-(10-1)*$D$59)*$D$43+$D$59</f>
         <v/>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>DSRA (Debt Service Reserve Account)</t>
         </is>
       </c>
-      <c r="B106" s="4" t="n"/>
-      <c r="C106" s="4" t="n"/>
-      <c r="D106" s="4" t="n"/>
-      <c r="E106" s="4" t="n"/>
-      <c r="F106" s="4" t="n"/>
-      <c r="G106" s="4" t="n"/>
-      <c r="H106" s="4" t="n"/>
-      <c r="I106" s="4" t="n"/>
-      <c r="J106" s="4" t="n"/>
-      <c r="K106" s="4" t="n"/>
-      <c r="L106" s="4" t="n"/>
-      <c r="M106" s="4" t="n"/>
-      <c r="N106" s="4" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Target</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
-        </is>
-      </c>
-      <c r="D107" s="18">
-        <f>E93*$D$45/12</f>
-        <v/>
-      </c>
-      <c r="E107" s="18">
-        <f>F93*$D$45/12</f>
-        <v/>
-      </c>
-      <c r="F107" s="18">
-        <f>G93*$D$45/12</f>
-        <v/>
-      </c>
-      <c r="G107" s="18">
-        <f>H93*$D$45/12</f>
-        <v/>
-      </c>
-      <c r="H107" s="18">
-        <f>I93*$D$45/12</f>
-        <v/>
-      </c>
-      <c r="I107" s="18">
-        <f>J93*$D$45/12</f>
-        <v/>
-      </c>
-      <c r="J107" s="18">
-        <f>K93*$D$45/12</f>
-        <v/>
-      </c>
-      <c r="K107" s="18">
-        <f>L93*$D$45/12</f>
-        <v/>
-      </c>
-      <c r="L107" s="18">
-        <f>M93*$D$45/12</f>
-        <v/>
-      </c>
-      <c r="M107" s="18">
-        <f>N93*$D$45/12</f>
-        <v/>
-      </c>
-      <c r="N107" s="18">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="4" t="n"/>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="n"/>
+      <c r="G107" s="4" t="n"/>
+      <c r="H107" s="4" t="n"/>
+      <c r="I107" s="4" t="n"/>
+      <c r="J107" s="4" t="n"/>
+      <c r="K107" s="4" t="n"/>
+      <c r="L107" s="4" t="n"/>
+      <c r="M107" s="4" t="n"/>
+      <c r="N107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Target</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
@@ -5815,56 +5338,60 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr"/>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
+        </is>
+      </c>
       <c r="D108" s="18">
+        <f>E93*$D$45/12</f>
+        <v/>
+      </c>
+      <c r="E108" s="18">
+        <f>F93*$D$45/12</f>
+        <v/>
+      </c>
+      <c r="F108" s="18">
+        <f>G93*$D$45/12</f>
+        <v/>
+      </c>
+      <c r="G108" s="18">
+        <f>H93*$D$45/12</f>
+        <v/>
+      </c>
+      <c r="H108" s="18">
+        <f>I93*$D$45/12</f>
+        <v/>
+      </c>
+      <c r="I108" s="18">
+        <f>J93*$D$45/12</f>
+        <v/>
+      </c>
+      <c r="J108" s="18">
+        <f>K93*$D$45/12</f>
+        <v/>
+      </c>
+      <c r="K108" s="18">
+        <f>L93*$D$45/12</f>
+        <v/>
+      </c>
+      <c r="L108" s="18">
+        <f>M93*$D$45/12</f>
+        <v/>
+      </c>
+      <c r="M108" s="18">
+        <f>N93*$D$45/12</f>
+        <v/>
+      </c>
+      <c r="N108" s="18">
         <f>0</f>
-        <v/>
-      </c>
-      <c r="E108" s="18">
-        <f>D98</f>
-        <v/>
-      </c>
-      <c r="F108" s="18">
-        <f>E98</f>
-        <v/>
-      </c>
-      <c r="G108" s="18">
-        <f>F98</f>
-        <v/>
-      </c>
-      <c r="H108" s="18">
-        <f>G98</f>
-        <v/>
-      </c>
-      <c r="I108" s="18">
-        <f>H98</f>
-        <v/>
-      </c>
-      <c r="J108" s="18">
-        <f>I98</f>
-        <v/>
-      </c>
-      <c r="K108" s="18">
-        <f>J98</f>
-        <v/>
-      </c>
-      <c r="L108" s="18">
-        <f>K98</f>
-        <v/>
-      </c>
-      <c r="M108" s="18">
-        <f>L98</f>
-        <v/>
-      </c>
-      <c r="N108" s="18">
-        <f>M98</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -5872,356 +5399,366 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>Target - Beginning</t>
-        </is>
-      </c>
+      <c r="C109" s="6" t="inlineStr"/>
       <c r="D109" s="18">
-        <f>D95-D96</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E109" s="18">
-        <f>E95-E96</f>
+        <f>D98</f>
         <v/>
       </c>
       <c r="F109" s="18">
-        <f>F95-F96</f>
+        <f>E98</f>
         <v/>
       </c>
       <c r="G109" s="18">
-        <f>G95-G96</f>
+        <f>F98</f>
         <v/>
       </c>
       <c r="H109" s="18">
-        <f>H95-H96</f>
+        <f>G98</f>
         <v/>
       </c>
       <c r="I109" s="18">
-        <f>I95-I96</f>
+        <f>H98</f>
         <v/>
       </c>
       <c r="J109" s="18">
-        <f>J95-J96</f>
+        <f>I98</f>
         <v/>
       </c>
       <c r="K109" s="18">
-        <f>K95-K96</f>
+        <f>J98</f>
         <v/>
       </c>
       <c r="L109" s="18">
-        <f>L95-L96</f>
+        <f>K98</f>
         <v/>
       </c>
       <c r="M109" s="18">
-        <f>M95-M96</f>
+        <f>L98</f>
         <v/>
       </c>
       <c r="N109" s="18">
-        <f>N95-N96</f>
+        <f>M98</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
+          <t>DSRA Funding/(Release)</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
+      <c r="D110" s="18">
+        <f>D95-D96</f>
+        <v/>
+      </c>
+      <c r="E110" s="18">
+        <f>E95-E96</f>
+        <v/>
+      </c>
+      <c r="F110" s="18">
+        <f>F95-F96</f>
+        <v/>
+      </c>
+      <c r="G110" s="18">
+        <f>G95-G96</f>
+        <v/>
+      </c>
+      <c r="H110" s="18">
+        <f>H95-H96</f>
+        <v/>
+      </c>
+      <c r="I110" s="18">
+        <f>I95-I96</f>
+        <v/>
+      </c>
+      <c r="J110" s="18">
+        <f>J95-J96</f>
+        <v/>
+      </c>
+      <c r="K110" s="18">
+        <f>K95-K96</f>
+        <v/>
+      </c>
+      <c r="L110" s="18">
+        <f>L95-L96</f>
+        <v/>
+      </c>
+      <c r="M110" s="18">
+        <f>M95-M96</f>
+        <v/>
+      </c>
+      <c r="N110" s="18">
+        <f>N95-N96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
           <t>DSRA Ending</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>Beginning + Funding</t>
         </is>
       </c>
-      <c r="D110" s="18">
+      <c r="D111" s="18">
         <f>D96+D97</f>
         <v/>
       </c>
-      <c r="E110" s="18">
+      <c r="E111" s="18">
         <f>E96+E97</f>
         <v/>
       </c>
-      <c r="F110" s="18">
+      <c r="F111" s="18">
         <f>F96+F97</f>
         <v/>
       </c>
-      <c r="G110" s="18">
+      <c r="G111" s="18">
         <f>G96+G97</f>
         <v/>
       </c>
-      <c r="H110" s="18">
+      <c r="H111" s="18">
         <f>H96+H97</f>
         <v/>
       </c>
-      <c r="I110" s="18">
+      <c r="I111" s="18">
         <f>I96+I97</f>
         <v/>
       </c>
-      <c r="J110" s="18">
+      <c r="J111" s="18">
         <f>J96+J97</f>
         <v/>
       </c>
-      <c r="K110" s="18">
+      <c r="K111" s="18">
         <f>K96+K97</f>
         <v/>
       </c>
-      <c r="L110" s="18">
+      <c r="L111" s="18">
         <f>L96+L97</f>
         <v/>
       </c>
-      <c r="M110" s="18">
+      <c r="M111" s="18">
         <f>M96+M97</f>
         <v/>
       </c>
-      <c r="N110" s="18">
+      <c r="N111" s="18">
         <f>N96+N97</f>
         <v/>
       </c>
     </row>
-    <row r="111"/>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
+    <row r="112"/>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>DISTRIBUTION WATERFALL</t>
         </is>
       </c>
-      <c r="B112" s="4" t="n"/>
-      <c r="C112" s="4" t="n"/>
-      <c r="D112" s="4" t="n"/>
-      <c r="E112" s="4" t="n"/>
-      <c r="F112" s="4" t="n"/>
-      <c r="G112" s="4" t="n"/>
-      <c r="H112" s="4" t="n"/>
-      <c r="I112" s="4" t="n"/>
-      <c r="J112" s="4" t="n"/>
-      <c r="K112" s="4" t="n"/>
-      <c r="L112" s="4" t="n"/>
-      <c r="M112" s="4" t="n"/>
-      <c r="N112" s="4" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>Cash Available for Distribution</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>CFADS - Total DS - DSRA Fund</t>
-        </is>
-      </c>
-      <c r="E113" s="18">
-        <f>E81-(E85+E90)-E97</f>
-        <v/>
-      </c>
-      <c r="F113" s="18">
-        <f>F81-(F85+F90)-F97</f>
-        <v/>
-      </c>
-      <c r="G113" s="18">
-        <f>G81-(G85+G90)-G97</f>
-        <v/>
-      </c>
-      <c r="H113" s="18">
-        <f>H81-(H85+H90)-H97</f>
-        <v/>
-      </c>
-      <c r="I113" s="18">
-        <f>I81-(I85+I90)-I97</f>
-        <v/>
-      </c>
-      <c r="J113" s="18">
-        <f>J81-(J85+J90)-J97</f>
-        <v/>
-      </c>
-      <c r="K113" s="18">
-        <f>K81-(K85+K90)-K97</f>
-        <v/>
-      </c>
-      <c r="L113" s="18">
-        <f>L81-(L85+L90)-L97</f>
-        <v/>
-      </c>
-      <c r="M113" s="18">
-        <f>M81-(M85+M90)-M97</f>
-        <v/>
-      </c>
-      <c r="N113" s="18">
-        <f>N81-(N85+N90)-N97</f>
-        <v/>
-      </c>
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="n"/>
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="n"/>
+      <c r="G113" s="4" t="n"/>
+      <c r="H113" s="4" t="n"/>
+      <c r="I113" s="4" t="n"/>
+      <c r="J113" s="4" t="n"/>
+      <c r="K113" s="4" t="n"/>
+      <c r="L113" s="4" t="n"/>
+      <c r="M113" s="4" t="n"/>
+      <c r="N113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Lock-up Test</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr"/>
+          <t>Cash Available for Distribution</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>PASS if DSCR ≥ Lock-up</t>
-        </is>
-      </c>
-      <c r="E114" s="22">
-        <f>IF(E92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="F114" s="22">
-        <f>IF(F92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="G114" s="22">
-        <f>IF(G92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="H114" s="22">
-        <f>IF(H92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="I114" s="22">
-        <f>IF(I92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="J114" s="22">
-        <f>IF(J92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="K114" s="22">
-        <f>IF(K92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="L114" s="22">
-        <f>IF(L92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="M114" s="22">
-        <f>IF(M92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="N114" s="22">
-        <f>IF(N92&gt;=$D$47,"PASS","LOCKED")</f>
+          <t>CFADS - Total DS - DSRA Fund</t>
+        </is>
+      </c>
+      <c r="E114" s="18">
+        <f>E81-(E85+E90)-E97</f>
+        <v/>
+      </c>
+      <c r="F114" s="18">
+        <f>F81-(F85+F90)-F97</f>
+        <v/>
+      </c>
+      <c r="G114" s="18">
+        <f>G81-(G85+G90)-G97</f>
+        <v/>
+      </c>
+      <c r="H114" s="18">
+        <f>H81-(H85+H90)-H97</f>
+        <v/>
+      </c>
+      <c r="I114" s="18">
+        <f>I81-(I85+I90)-I97</f>
+        <v/>
+      </c>
+      <c r="J114" s="18">
+        <f>J81-(J85+J90)-J97</f>
+        <v/>
+      </c>
+      <c r="K114" s="18">
+        <f>K81-(K85+K90)-K97</f>
+        <v/>
+      </c>
+      <c r="L114" s="18">
+        <f>L81-(L85+L90)-L97</f>
+        <v/>
+      </c>
+      <c r="M114" s="18">
+        <f>M81-(M85+M90)-M97</f>
+        <v/>
+      </c>
+      <c r="N114" s="18">
+        <f>N81-(N85+N90)-N97</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
+          <t>Lock-up Test</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr"/>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>PASS if DSCR ≥ Lock-up</t>
+        </is>
+      </c>
+      <c r="E115" s="22">
+        <f>IF(E92&gt;=$D$47,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="F115" s="22">
+        <f>IF(F92&gt;=$D$47,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="G115" s="22">
+        <f>IF(G92&gt;=$D$47,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H115" s="22">
+        <f>IF(H92&gt;=$D$47,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I115" s="22">
+        <f>IF(I92&gt;=$D$47,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J115" s="22">
+        <f>IF(J92&gt;=$D$47,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K115" s="22">
+        <f>IF(K92&gt;=$D$47,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L115" s="22">
+        <f>IF(L92&gt;=$D$47,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M115" s="22">
+        <f>IF(M92&gt;=$D$47,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N115" s="22">
+        <f>IF(N92&gt;=$D$47,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
           <t>Distributable Cash</t>
         </is>
       </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>If PASS, MAX(0, Cash Avail)</t>
         </is>
       </c>
-      <c r="E115" s="7">
-        <f>IF(E102="PASS",MAX(0,E101),0)</f>
-        <v/>
-      </c>
-      <c r="F115" s="7">
-        <f>IF(F102="PASS",MAX(0,F101),0)</f>
-        <v/>
-      </c>
-      <c r="G115" s="7">
-        <f>IF(G102="PASS",MAX(0,G101),0)</f>
-        <v/>
-      </c>
-      <c r="H115" s="7">
-        <f>IF(H102="PASS",MAX(0,H101),0)</f>
-        <v/>
-      </c>
-      <c r="I115" s="7">
-        <f>IF(I102="PASS",MAX(0,I101),0)</f>
-        <v/>
-      </c>
-      <c r="J115" s="7">
-        <f>IF(J102="PASS",MAX(0,J101),0)</f>
-        <v/>
-      </c>
-      <c r="K115" s="7">
-        <f>IF(K102="PASS",MAX(0,K101),0)</f>
-        <v/>
-      </c>
-      <c r="L115" s="7">
-        <f>IF(L102="PASS",MAX(0,L101),0)</f>
-        <v/>
-      </c>
-      <c r="M115" s="7">
-        <f>IF(M102="PASS",MAX(0,M101),0)</f>
-        <v/>
-      </c>
-      <c r="N115" s="7">
-        <f>IF(N102="PASS",MAX(0,N101),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116"/>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="E116" s="7" t="inlineStr"/>
+      <c r="F116" s="7" t="inlineStr"/>
+      <c r="G116" s="7" t="inlineStr"/>
+      <c r="H116" s="7" t="inlineStr"/>
+      <c r="I116" s="7" t="inlineStr"/>
+      <c r="J116" s="7" t="inlineStr"/>
+      <c r="K116" s="7" t="inlineStr"/>
+      <c r="L116" s="7" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+      <c r="N116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>SOURCES &amp; USES (Year 0)</t>
         </is>
       </c>
-      <c r="B117" s="4" t="n"/>
-      <c r="C117" s="4" t="n"/>
-      <c r="D117" s="4" t="n"/>
-      <c r="E117" s="4" t="n"/>
-      <c r="F117" s="4" t="n"/>
-      <c r="G117" s="4" t="n"/>
-      <c r="H117" s="4" t="n"/>
-      <c r="I117" s="4" t="n"/>
-      <c r="J117" s="4" t="n"/>
-      <c r="K117" s="4" t="n"/>
-      <c r="L117" s="4" t="n"/>
-      <c r="M117" s="4" t="n"/>
-      <c r="N117" s="4" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="23" t="inlineStr">
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="4" t="n"/>
+      <c r="D118" s="4" t="n"/>
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="4" t="n"/>
+      <c r="G118" s="4" t="n"/>
+      <c r="H118" s="4" t="n"/>
+      <c r="I118" s="4" t="n"/>
+      <c r="J118" s="4" t="n"/>
+      <c r="K118" s="4" t="n"/>
+      <c r="L118" s="4" t="n"/>
+      <c r="M118" s="4" t="n"/>
+      <c r="N118" s="4" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="23" t="inlineStr">
         <is>
           <t>USES</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr"/>
-      <c r="C118" s="6" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Purchase Price</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B119" s="6" t="inlineStr"/>
       <c r="C119" s="6" t="inlineStr"/>
-      <c r="D119" s="18">
-        <f>$D$17</f>
-        <v/>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Transaction Fees</t>
+          <t xml:space="preserve">  Purchase Price</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
@@ -6231,14 +5768,14 @@
       </c>
       <c r="C120" s="6" t="inlineStr"/>
       <c r="D120" s="18">
-        <f>$D$17*$D$18</f>
+        <f>$D$17</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DSRA Funding</t>
+          <t xml:space="preserve">  Transaction Fees</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
@@ -6248,58 +5785,58 @@
       </c>
       <c r="C121" s="6" t="inlineStr"/>
       <c r="D121" s="18">
-        <f>D95</f>
+        <f>$D$17*$D$18</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  DSRA Funding</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr"/>
+      <c r="D122" s="18">
+        <f>D95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
           <t>Total Uses</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr"/>
-      <c r="D122" s="7">
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr"/>
+      <c r="D123" s="7">
         <f>D107+D108+D109</f>
         <v/>
       </c>
     </row>
-    <row r="123"/>
-    <row r="124">
-      <c r="A124" s="23" t="inlineStr">
+    <row r="124"/>
+    <row r="125">
+      <c r="A125" s="23" t="inlineStr">
         <is>
           <t>SOURCES</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr"/>
-      <c r="C124" s="6" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Debt</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B125" s="6" t="inlineStr"/>
       <c r="C125" s="6" t="inlineStr"/>
-      <c r="D125" s="18">
-        <f>$D$57</f>
-        <v/>
-      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Equity</t>
+          <t xml:space="preserve">  Debt</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
@@ -6307,20 +5844,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>Plug to balance</t>
-        </is>
-      </c>
+      <c r="C126" s="6" t="inlineStr"/>
       <c r="D126" s="18">
-        <f>D110-D113</f>
+        <f>$D$57</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Total Sources</t>
+          <t xml:space="preserve">  Equity</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
@@ -6328,71 +5861,71 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr"/>
-      <c r="D127" s="7">
-        <f>D113+D114</f>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>Plug to balance</t>
+        </is>
+      </c>
+      <c r="D127" s="18">
+        <f>D110-D113</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
+          <t>Total Sources</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr"/>
+      <c r="D128" s="7">
+        <f>D113+D114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
           <t>Balance Check</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr"/>
-      <c r="C128" s="6" t="inlineStr"/>
-      <c r="D128" s="10">
+      <c r="B129" s="6" t="inlineStr"/>
+      <c r="C129" s="6" t="inlineStr"/>
+      <c r="D129" s="10">
         <f>IF(ABS(D110-D115)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="129"/>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>EXIT CALCULATIONS</t>
         </is>
       </c>
-      <c r="B130" s="4" t="n"/>
-      <c r="C130" s="4" t="n"/>
-      <c r="D130" s="4" t="n"/>
-      <c r="E130" s="4" t="n"/>
-      <c r="F130" s="4" t="n"/>
-      <c r="G130" s="4" t="n"/>
-      <c r="H130" s="4" t="n"/>
-      <c r="I130" s="4" t="n"/>
-      <c r="J130" s="4" t="n"/>
-      <c r="K130" s="4" t="n"/>
-      <c r="L130" s="4" t="n"/>
-      <c r="M130" s="4" t="n"/>
-      <c r="N130" s="4" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>Exit EV</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>Exit Multiple × Exit Yr EBITDA</t>
-        </is>
-      </c>
-      <c r="K131" s="18">
-        <f>$D$19*K75</f>
-        <v/>
-      </c>
+      <c r="B131" s="4" t="n"/>
+      <c r="C131" s="4" t="n"/>
+      <c r="D131" s="4" t="n"/>
+      <c r="E131" s="4" t="n"/>
+      <c r="F131" s="4" t="n"/>
+      <c r="G131" s="4" t="n"/>
+      <c r="H131" s="4" t="n"/>
+      <c r="I131" s="4" t="n"/>
+      <c r="J131" s="4" t="n"/>
+      <c r="K131" s="4" t="n"/>
+      <c r="L131" s="4" t="n"/>
+      <c r="M131" s="4" t="n"/>
+      <c r="N131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Exit Debt Payoff</t>
+          <t>Exit EV</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
@@ -6402,18 +5935,15 @@
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Ending Bal at Exit</t>
-        </is>
-      </c>
-      <c r="K132" s="18">
-        <f>K91</f>
-        <v/>
-      </c>
+          <t>Exit Multiple × Exit Yr EBITDA</t>
+        </is>
+      </c>
+      <c r="K132" s="18" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>DSRA Release</t>
+          <t>Exit Debt Payoff</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
@@ -6423,243 +5953,211 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>DSRA Ending at Exit</t>
+          <t>Ending Bal at Exit</t>
         </is>
       </c>
       <c r="K133" s="18">
-        <f>K98</f>
+        <f>K91</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
+          <t>DSRA Release</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>DSRA Ending at Exit</t>
+        </is>
+      </c>
+      <c r="K134" s="18">
+        <f>K98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
           <t>Exit Equity Proceeds</t>
         </is>
       </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
         <is>
           <t>Exit EV - Debt + DSRA</t>
         </is>
       </c>
-      <c r="K134" s="7">
-        <f>K119-K120+K121</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135"/>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
+      <c r="K135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136"/>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>EQUITY RETURNS</t>
         </is>
       </c>
-      <c r="B136" s="4" t="n"/>
-      <c r="C136" s="4" t="n"/>
-      <c r="D136" s="4" t="n"/>
-      <c r="E136" s="4" t="n"/>
-      <c r="F136" s="4" t="n"/>
-      <c r="G136" s="4" t="n"/>
-      <c r="H136" s="4" t="n"/>
-      <c r="I136" s="4" t="n"/>
-      <c r="J136" s="4" t="n"/>
-      <c r="K136" s="4" t="n"/>
-      <c r="L136" s="4" t="n"/>
-      <c r="M136" s="4" t="n"/>
-      <c r="N136" s="4" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>Equity Cash Flow</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr"/>
-      <c r="D137" s="18">
-        <f>-D114</f>
-        <v/>
-      </c>
-      <c r="E137" s="18">
-        <f>E103</f>
-        <v/>
-      </c>
-      <c r="F137" s="18">
-        <f>F103</f>
-        <v/>
-      </c>
-      <c r="G137" s="18">
-        <f>G103</f>
-        <v/>
-      </c>
-      <c r="H137" s="18">
-        <f>H103</f>
-        <v/>
-      </c>
-      <c r="I137" s="18">
-        <f>I103</f>
-        <v/>
-      </c>
-      <c r="J137" s="18">
-        <f>J103</f>
-        <v/>
-      </c>
-      <c r="K137" s="18">
-        <f>K103+K122</f>
-        <v/>
-      </c>
-      <c r="L137" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M137" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N137" s="18">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="4" t="n"/>
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" s="4" t="n"/>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="4" t="n"/>
+      <c r="J137" s="4" t="n"/>
+      <c r="K137" s="4" t="n"/>
+      <c r="L137" s="4" t="n"/>
+      <c r="M137" s="4" t="n"/>
+      <c r="N137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
+          <t>Equity Cash Flow</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr"/>
-      <c r="D138" s="31">
-        <f>IRR(D125:K125)</f>
-        <v/>
-      </c>
+      <c r="D138" s="18" t="inlineStr"/>
+      <c r="E138" s="18" t="inlineStr"/>
+      <c r="F138" s="18" t="inlineStr"/>
+      <c r="G138" s="18" t="inlineStr"/>
+      <c r="H138" s="18" t="inlineStr"/>
+      <c r="I138" s="18" t="inlineStr"/>
+      <c r="J138" s="18" t="inlineStr"/>
+      <c r="K138" s="18" t="inlineStr"/>
+      <c r="L138" s="18" t="inlineStr"/>
+      <c r="M138" s="18" t="inlineStr"/>
+      <c r="N138" s="18" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr"/>
+      <c r="D139" s="31" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
           <t>MOIC</t>
         </is>
       </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="B140" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr">
+      <c r="C140" s="6" t="inlineStr">
         <is>
           <t>Sum inflows / outflow</t>
         </is>
       </c>
-      <c r="D139" s="30">
-        <f>SUMIF(D125:K125,"&gt;0")/ABS(D125)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140"/>
-    <row r="141">
-      <c r="A141" s="23" t="inlineStr">
+      <c r="D140" s="30" t="inlineStr"/>
+    </row>
+    <row r="141"/>
+    <row r="142">
+      <c r="A142" s="23" t="inlineStr">
         <is>
           <t>Unlevered Returns (for reference)</t>
         </is>
       </c>
-      <c r="B141" s="6" t="inlineStr"/>
-      <c r="C141" s="6" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered Cash Flow</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B142" s="6" t="inlineStr"/>
       <c r="C142" s="6" t="inlineStr"/>
-      <c r="D142" s="18">
-        <f>-$D$17-D108</f>
-        <v/>
-      </c>
-      <c r="E142" s="18">
-        <f>E81</f>
-        <v/>
-      </c>
-      <c r="F142" s="18">
-        <f>F81</f>
-        <v/>
-      </c>
-      <c r="G142" s="18">
-        <f>G81</f>
-        <v/>
-      </c>
-      <c r="H142" s="18">
-        <f>H81</f>
-        <v/>
-      </c>
-      <c r="I142" s="18">
-        <f>I81</f>
-        <v/>
-      </c>
-      <c r="J142" s="18">
-        <f>J81</f>
-        <v/>
-      </c>
-      <c r="K142" s="18">
-        <f>K81+K119</f>
-        <v/>
-      </c>
-      <c r="L142" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M142" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N142" s="18">
-        <f>0</f>
-        <v/>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
+          <t>Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr"/>
+      <c r="D143" s="18">
+        <f>-$D$17-D108</f>
+        <v/>
+      </c>
+      <c r="E143" s="18">
+        <f>E81</f>
+        <v/>
+      </c>
+      <c r="F143" s="18">
+        <f>F81</f>
+        <v/>
+      </c>
+      <c r="G143" s="18">
+        <f>G81</f>
+        <v/>
+      </c>
+      <c r="H143" s="18">
+        <f>H81</f>
+        <v/>
+      </c>
+      <c r="I143" s="18">
+        <f>I81</f>
+        <v/>
+      </c>
+      <c r="J143" s="18">
+        <f>J81</f>
+        <v/>
+      </c>
+      <c r="K143" s="18">
+        <f>K81+K119</f>
+        <v/>
+      </c>
+      <c r="L143" s="18">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M143" s="18">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N143" s="18">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
           <t>Unlevered IRR</t>
         </is>
       </c>
-      <c r="B143" s="6" t="inlineStr">
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr"/>
-      <c r="D143" s="31">
-        <f>IRR(D130:K130)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
+      <c r="C144" s="6" t="inlineStr"/>
+      <c r="D144" s="31" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -6683,7 +6181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N151"/>
+  <dimension ref="A1:N149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7078,8 +6576,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -7180,7 +6676,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -7301,7 +6796,6 @@
         <v>400</v>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -7402,7 +6896,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -7503,7 +6996,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
@@ -7644,7 +7136,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
@@ -7725,7 +7216,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
@@ -7851,7 +7341,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
@@ -8043,7 +7532,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
@@ -8211,7 +7699,6 @@
         <v/>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
@@ -8506,7 +7993,6 @@
         <v/>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
@@ -8560,7 +8046,6 @@
         <v/>
       </c>
     </row>
-    <row r="88"/>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
@@ -8809,7 +8294,6 @@
         <v/>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -9656,7 +9140,6 @@
         <v/>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
@@ -9844,7 +9327,6 @@
         <v/>
       </c>
     </row>
-    <row r="116"/>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
@@ -9981,8 +9463,6 @@
         </is>
       </c>
     </row>
-    <row r="126"/>
-    <row r="127"/>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
@@ -10000,7 +9480,6 @@
         <v/>
       </c>
     </row>
-    <row r="129"/>
     <row r="130">
       <c r="A130" s="23" t="inlineStr">
         <is>
@@ -10078,7 +9557,6 @@
         <v/>
       </c>
     </row>
-    <row r="135"/>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
@@ -10183,7 +9661,6 @@
         <v/>
       </c>
     </row>
-    <row r="141"/>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
@@ -10299,7 +9776,6 @@
         <v/>
       </c>
     </row>
-    <row r="146"/>
     <row r="147">
       <c r="A147" s="23" t="inlineStr">
         <is>
@@ -10383,8 +9859,6 @@
         <v/>
       </c>
     </row>
-    <row r="150"/>
-    <row r="151"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +97,14 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -154,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,6 +241,8 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3016,7 +3026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N144"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3098,21 +3108,45 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="57" t="inlineStr">
-        <is>
-          <t>═══ DRILL MODE: Key formulas blanked. Rebuild using Formula Logic hints in Column C. ═══</t>
-        </is>
-      </c>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE - Fill in yellow cells ═══</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>═══ AUDIT STRIP ═══</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Entry EV</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price for asset</t>
+        </is>
+      </c>
+      <c r="D3" s="7">
+        <f>$D$28</f>
+        <v/>
+      </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -3121,13 +3155,17 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
+      <c r="M3" s="58" t="inlineStr">
+        <is>
+          <t>IRR Sensitivity:</t>
+        </is>
+      </c>
       <c r="N3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Entry EV</t>
+          <t>Y1 EBITDA</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3135,235 +3173,259 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
+      </c>
       <c r="D4" s="7">
-        <f>$D$17</f>
-        <v/>
+        <f>E87</f>
+        <v/>
+      </c>
+      <c r="M4" s="59" t="inlineStr">
+        <is>
+          <t>+/- 5% Entry → ~+/- 1% IRR</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Y1 EBITDA</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="49" t="n"/>
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="M5" s="59" t="inlineStr">
+        <is>
+          <t>+/- 0.5x Exit → ~+/- 1.5% IRR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
-        <is>
-          <t>═══════════ CONTROL PANEL ═══════════</t>
-        </is>
-      </c>
+      <c r="A6" s="49" t="n"/>
       <c r="B6" s="49" t="n"/>
       <c r="C6" s="49" t="n"/>
       <c r="D6" s="49" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="n"/>
+      <c r="A7" s="50" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
       <c r="B7" s="49" t="n"/>
       <c r="C7" s="49" t="n"/>
       <c r="D7" s="49" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>Revenue Mode</t>
         </is>
       </c>
       <c r="B8" s="49" t="n"/>
-      <c r="C8" s="49" t="n"/>
-      <c r="D8" s="49" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Merchant / Contracted / Hybrid</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
         <is>
-          <t>Revenue Mode</t>
+          <t>Contract End Year</t>
         </is>
       </c>
       <c r="B9" s="49" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D9" s="47" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
-        <is>
-          <t>Contract End Year</t>
-        </is>
-      </c>
+      <c r="A10" s="49" t="n"/>
       <c r="B10" s="49" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>0 = pure merchant; else year PPA ends</t>
-        </is>
-      </c>
-      <c r="D10" s="47" t="n">
-        <v>0</v>
-      </c>
+      <c r="C10" s="49" t="n"/>
+      <c r="D10" s="49" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="n"/>
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
       <c r="B11" s="49" t="n"/>
       <c r="C11" s="49" t="n"/>
       <c r="D11" s="49" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
-        <is>
-          <t>TIMING</t>
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B12" s="49" t="n"/>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="49" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
         <is>
-          <t>Exit Year</t>
+          <t>Tax Credit End Year</t>
         </is>
       </c>
       <c r="B13" s="49" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>5 / 7 / 10</t>
+          <t>0 = N/A; else last year of PTC/ITC</t>
         </is>
       </c>
       <c r="D13" s="47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>Tax Credit End Year</t>
-        </is>
-      </c>
+      <c r="A14" s="49" t="n"/>
       <c r="B14" s="49" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>0 = N/A; else last year of PTC/ITC</t>
-        </is>
-      </c>
-      <c r="D14" s="47" t="n">
-        <v>0</v>
-      </c>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="49" t="n"/>
+      <c r="A15" s="50" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
       <c r="B15" s="49" t="n"/>
       <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
+      <c r="D15" s="51" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="inlineStr">
-        <is>
-          <t>DEBT</t>
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>Debt Sweep</t>
         </is>
       </c>
       <c r="B16" s="49" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="51" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>Debt Sweep</t>
+          <t>Sweep %</t>
         </is>
       </c>
       <c r="B17" s="49" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>ON / OFF (for sweep assets)</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="inlineStr">
-        <is>
-          <t>ON</t>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t>Sweep %</t>
-        </is>
-      </c>
+      <c r="A18" s="49" t="n"/>
       <c r="B18" s="49" t="n"/>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Active when Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="52" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="49" t="n"/>
+      <c r="A19" s="50" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
       <c r="B19" s="49" t="n"/>
       <c r="C19" s="49" t="n"/>
-      <c r="D19" s="52" t="n"/>
+      <c r="D19" s="53" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>Carbon Region</t>
         </is>
       </c>
       <c r="B20" s="49" t="n"/>
-      <c r="C20" s="49" t="n"/>
-      <c r="D20" s="53" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>None / CARB / RGGI (thermal only)</t>
+        </is>
+      </c>
+      <c r="D20" s="47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>Carbon Region</t>
-        </is>
-      </c>
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>Exit Method</t>
+        </is>
+      </c>
+      <c r="B21" s="49" t="n"/>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>None / CARB / RGGI (thermal only)</t>
+          <t>Multiple / DCF</t>
         </is>
       </c>
       <c r="D21" s="47" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="54" t="inlineStr">
-        <is>
-          <t>Exit Method</t>
-        </is>
-      </c>
-      <c r="B22" s="49" t="n"/>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Multiple / DCF</t>
-        </is>
-      </c>
-      <c r="D22" s="47" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="10">
+        <f>D116</f>
+        <v/>
       </c>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
@@ -3377,52 +3439,81 @@
       <c r="N22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Debt Payoff Y7</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
       <c r="D23" s="10">
-        <f>D116</f>
+        <f>IF(K91&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Debt Payoff Y7</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr"/>
-      <c r="C24" s="6" t="inlineStr"/>
+          <t>Min DSCR ≥ 1.25x</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
       <c r="D24" s="10">
-        <f>IF(K91&lt;1,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR ≥ 1.25x</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr"/>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="10" t="n"/>
     </row>
     <row r="26"/>
-    <row r="27"/>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TRANSACTION INPUTS</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TRANSACTION INPUTS</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Entry EV</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>110</v>
+      </c>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
@@ -3437,93 +3528,108 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Entry EV</t>
+          <t>Transaction Fees</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Purchase price</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>110</v>
+          <t>Legal, advisory, financing</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Transaction Fees</t>
+          <t>Exit Multiple</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Legal, advisory, financing</t>
-        </is>
-      </c>
-      <c r="D30" s="32" t="n">
-        <v>0.015</v>
+          <t>On exit year EBITDA</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Exit Multiple</t>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>On exit year EBITDA</t>
-        </is>
-      </c>
-      <c r="D31" s="33" t="n">
+          <t>Hold period</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Exit Year</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Hold period</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33"/>
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="14" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>ASSET INPUTS</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+    </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>ASSET INPUTS</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Nameplate rating</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>200</v>
+      </c>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
@@ -3538,47 +3644,47 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Heat Rate</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>Btu/kWh</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Nameplate rating</t>
+          <t>Less efficient than CCGT</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>200</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Heat Rate</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Btu/kWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Less efficient than CCGT</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>10500</v>
+          <t>For UCAP accreditation</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Forced Outage Rate</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -3588,63 +3694,78 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>For UCAP accreditation</t>
+          <t>Unplanned downtime</t>
         </is>
       </c>
       <c r="D37" s="32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Forced Outage Rate</t>
+          <t>Dispatch Hours</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>hours/yr</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Unplanned downtime</t>
-        </is>
-      </c>
-      <c r="D38" s="32" t="n">
-        <v>0.05</v>
+          <t>Peak hours only (~400)</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Dispatch Hours</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>hours/yr</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Peak hours only (~400)</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="40"/>
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="14" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>PRICING INPUTS</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+    </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>PRICING INPUTS</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Power Price Y1</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>$/MWh</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Higher (dispatch-weighted)</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>95</v>
+      </c>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
@@ -3659,93 +3780,108 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Power Price Y1</t>
+          <t>Capacity Price Y1</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>$/MWh</t>
+          <t>$/kW-yr</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Higher (dispatch-weighted)</t>
+          <t>ICAP/RPM result</t>
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Capacity Price Y1</t>
+          <t>Gas Price Y1</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr</t>
+          <t>$/mmBtu</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>ICAP/RPM result</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>60</v>
+          <t>Henry Hub + basis</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Gas Price Y1</t>
+          <t>Escalation</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>$/mmBtu</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Henry Hub + basis</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="n">
-        <v>3.25</v>
+          <t>Applied to all prices/costs</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Escalation</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>%/yr</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Applied to all prices/costs</t>
-        </is>
-      </c>
-      <c r="D45" s="32" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="46"/>
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="32" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>COST INPUTS</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+    </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>COST INPUTS</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>VOM</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>$/MWh</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Variable O&amp;M</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="n">
+        <v>4</v>
+      </c>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
@@ -3760,93 +3896,108 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>VOM</t>
+          <t>FOM</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>$/MWh</t>
+          <t>$/kW-yr</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Variable O&amp;M</t>
+          <t>Fixed O&amp;M</t>
         </is>
       </c>
       <c r="D48" s="15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>FOM</t>
+          <t>Major Maintenance Year</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="n">
-        <v>12</v>
+          <t>Hot gas path inspection</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Major Maintenance Year</t>
+          <t>Major Maintenance Cost</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Hot gas path inspection</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>5</v>
+          <t>HGP inspection cost</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Major Maintenance Cost</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>HGP inspection cost</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52"/>
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="11" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>FINANCING INPUTS</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+    </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>FINANCING INPUTS</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Leverage</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Debt / Entry EV (lower)</t>
+        </is>
+      </c>
+      <c r="D53" s="32" t="n">
+        <v>0.3</v>
+      </c>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
@@ -3861,7 +4012,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Leverage</t>
+          <t>Interest Rate</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -3871,123 +4022,138 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Debt / Entry EV (lower)</t>
+          <t>All-in borrowing cost</t>
         </is>
       </c>
       <c r="D54" s="32" t="n">
-        <v>0.3</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Debt Tenor</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>All-in borrowing cost</t>
-        </is>
-      </c>
-      <c r="D55" s="32" t="n">
-        <v>0.07000000000000001</v>
+          <t>Amortization period</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Debt Tenor</t>
+          <t>DSRA Months</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Amortization period</t>
+          <t>Debt service reserve</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>DSRA Months</t>
+          <t>Cash Sweep %</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Debt service reserve</t>
-        </is>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>6</v>
+          <t>Lower for maint reserves</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep %</t>
+          <t>Lock-up DSCR</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Distribution threshold</t>
+        </is>
+      </c>
+      <c r="D58" s="33" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="33" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TAX INPUTS</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Tax Rate</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Lower for maint reserves</t>
-        </is>
-      </c>
-      <c r="D58" s="32" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Lock-up DSCR</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Distribution threshold</t>
-        </is>
-      </c>
-      <c r="D59" s="33" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>TAX INPUTS</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="n"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Blended federal + state</t>
+        </is>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>0.25</v>
+      </c>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
@@ -4002,7 +4168,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Tax Rate</t>
+          <t>Depreciable Basis</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -4012,63 +4178,79 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Blended federal + state</t>
+          <t>% of EV for depreciation</t>
         </is>
       </c>
       <c r="D62" s="32" t="n">
-        <v>0.25</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Depreciable Basis</t>
+          <t>Depreciation Life</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>% of EV for depreciation</t>
-        </is>
-      </c>
-      <c r="D63" s="32" t="n">
-        <v>0.85</v>
+          <t>Straight-line</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>Depreciation Life</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Straight-line</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65"/>
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="14" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>CALCULATED ITEMS</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="n"/>
+      <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="n"/>
+      <c r="J65" s="4" t="n"/>
+      <c r="K65" s="4" t="n"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n"/>
+      <c r="N65" s="4" t="n"/>
+    </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>CALCULATED ITEMS</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="n"/>
-      <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="n"/>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>UCAP (Unforced Capacity)</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Capacity × (1 - FOR)</t>
+        </is>
+      </c>
+      <c r="D66" s="16">
+        <f>$D$34*(1-$D$37)</f>
+        <v/>
+      </c>
       <c r="E66" s="4" t="n"/>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n"/>
@@ -4083,49 +4265,49 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>UCAP (Unforced Capacity)</t>
+          <t>Annual Generation</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>MWh</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Capacity × (1 - FOR)</t>
-        </is>
-      </c>
-      <c r="D67" s="16">
-        <f>$D$23*(1-$D$26)</f>
+          <t>Capacity × Hours × Avail</t>
+        </is>
+      </c>
+      <c r="D67" s="17">
+        <f>$D$34*$D$38*$D$36</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Annual Generation</t>
+          <t>Debt Amount</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>MWh</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Capacity × Hours × Avail</t>
-        </is>
-      </c>
-      <c r="D68" s="17">
-        <f>$D$23*$D$27*$D$25</f>
+          <t>Entry EV × Leverage</t>
+        </is>
+      </c>
+      <c r="D68" s="18">
+        <f>$D$28*$D$53</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Debt Amount</t>
+          <t>Annual Depreciation</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -4135,83 +4317,128 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Entry EV × Leverage</t>
+          <t>EV × Basis / Life</t>
         </is>
       </c>
       <c r="D69" s="18">
-        <f>$D$17*$D$42</f>
+        <f>$D$28*$D$62/$D$63</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Annual Depreciation</t>
+          <t>Scheduled Principal</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>$mm/yr</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>EV × Basis / Life</t>
+          <t>Debt / Tenor</t>
         </is>
       </c>
       <c r="D70" s="18">
-        <f>$D$17*$D$51/$D$52</f>
+        <f>$D$68/$D$55</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>Scheduled Principal</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>$mm/yr</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Debt / Tenor</t>
-        </is>
-      </c>
-      <c r="D71" s="18" t="inlineStr"/>
-    </row>
-    <row r="72"/>
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="18" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>OPERATING MODEL</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n"/>
+    </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING MODEL</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Power Price</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>$/MWh</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Escalated</t>
+        </is>
+      </c>
       <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="n"/>
+      <c r="E73" s="18">
+        <f>$D$41*(1+$D$44)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F73" s="18">
+        <f>$D$41*(1+$D$44)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G73" s="18">
+        <f>$D$41*(1+$D$44)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H73" s="18">
+        <f>$D$41*(1+$D$44)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I73" s="18">
+        <f>$D$41*(1+$D$44)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J73" s="18">
+        <f>$D$41*(1+$D$44)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="K73" s="18">
+        <f>$D$41*(1+$D$44)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="L73" s="18">
+        <f>$D$41*(1+$D$44)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="M73" s="18">
+        <f>$D$41*(1+$D$44)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="N73" s="18">
+        <f>$D$41*(1+$D$44)^(10-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Power Price</t>
+          <t>Capacity Price</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>$/MWh</t>
+          <t>$/kW-yr</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -4220,55 +4447,55 @@
         </is>
       </c>
       <c r="E74" s="18">
-        <f>$D$30*(1+$D$33)^(1-1)</f>
+        <f>$D$42*(1+$D$44)^(1-1)</f>
         <v/>
       </c>
       <c r="F74" s="18">
-        <f>$D$30*(1+$D$33)^(2-1)</f>
+        <f>$D$42*(1+$D$44)^(2-1)</f>
         <v/>
       </c>
       <c r="G74" s="18">
-        <f>$D$30*(1+$D$33)^(3-1)</f>
+        <f>$D$42*(1+$D$44)^(3-1)</f>
         <v/>
       </c>
       <c r="H74" s="18">
-        <f>$D$30*(1+$D$33)^(4-1)</f>
+        <f>$D$42*(1+$D$44)^(4-1)</f>
         <v/>
       </c>
       <c r="I74" s="18">
-        <f>$D$30*(1+$D$33)^(5-1)</f>
+        <f>$D$42*(1+$D$44)^(5-1)</f>
         <v/>
       </c>
       <c r="J74" s="18">
-        <f>$D$30*(1+$D$33)^(6-1)</f>
+        <f>$D$42*(1+$D$44)^(6-1)</f>
         <v/>
       </c>
       <c r="K74" s="18">
-        <f>$D$30*(1+$D$33)^(7-1)</f>
+        <f>$D$42*(1+$D$44)^(7-1)</f>
         <v/>
       </c>
       <c r="L74" s="18">
-        <f>$D$30*(1+$D$33)^(8-1)</f>
+        <f>$D$42*(1+$D$44)^(8-1)</f>
         <v/>
       </c>
       <c r="M74" s="18">
-        <f>$D$30*(1+$D$33)^(9-1)</f>
+        <f>$D$42*(1+$D$44)^(9-1)</f>
         <v/>
       </c>
       <c r="N74" s="18">
-        <f>$D$30*(1+$D$33)^(10-1)</f>
+        <f>$D$42*(1+$D$44)^(10-1)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Capacity Price</t>
+          <t>Gas Price</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr</t>
+          <t>$/mmBtu</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -4276,109 +4503,93 @@
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E75" s="18">
-        <f>$D$31*(1+$D$33)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F75" s="18">
-        <f>$D$31*(1+$D$33)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G75" s="18">
-        <f>$D$31*(1+$D$33)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H75" s="18">
-        <f>$D$31*(1+$D$33)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I75" s="18">
-        <f>$D$31*(1+$D$33)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J75" s="18">
-        <f>$D$31*(1+$D$33)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K75" s="18">
-        <f>$D$31*(1+$D$33)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L75" s="18">
-        <f>$D$31*(1+$D$33)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M75" s="18">
-        <f>$D$31*(1+$D$33)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N75" s="18">
-        <f>$D$31*(1+$D$33)^(10-1)</f>
+      <c r="E75" s="19">
+        <f>$D$43*(1+$D$44)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F75" s="19">
+        <f>$D$43*(1+$D$44)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G75" s="19">
+        <f>$D$43*(1+$D$44)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H75" s="19">
+        <f>$D$43*(1+$D$44)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I75" s="19">
+        <f>$D$43*(1+$D$44)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J75" s="19">
+        <f>$D$43*(1+$D$44)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="K75" s="19">
+        <f>$D$43*(1+$D$44)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="L75" s="19">
+        <f>$D$43*(1+$D$44)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="M75" s="19">
+        <f>$D$43*(1+$D$44)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="N75" s="19">
+        <f>$D$43*(1+$D$44)^(10-1)</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Gas Price</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>$/mmBtu</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Escalated</t>
-        </is>
-      </c>
-      <c r="E76" s="19">
-        <f>$D$32*(1+$D$33)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F76" s="19">
-        <f>$D$32*(1+$D$33)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G76" s="19">
-        <f>$D$32*(1+$D$33)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H76" s="19">
-        <f>$D$32*(1+$D$33)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I76" s="19">
-        <f>$D$32*(1+$D$33)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J76" s="19">
-        <f>$D$32*(1+$D$33)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K76" s="19">
-        <f>$D$32*(1+$D$33)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L76" s="19">
-        <f>$D$32*(1+$D$33)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M76" s="19">
-        <f>$D$32*(1+$D$33)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N76" s="19">
-        <f>$D$32*(1+$D$33)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77"/>
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="E76" s="19" t="n"/>
+      <c r="F76" s="19" t="n"/>
+      <c r="G76" s="19" t="n"/>
+      <c r="H76" s="19" t="n"/>
+      <c r="I76" s="19" t="n"/>
+      <c r="J76" s="19" t="n"/>
+      <c r="K76" s="19" t="n"/>
+      <c r="L76" s="19" t="n"/>
+      <c r="M76" s="19" t="n"/>
+      <c r="N76" s="19" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Energy Revenue</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Generation × Power Price / 1M</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="18" t="n"/>
+      <c r="G77" s="18" t="n"/>
+      <c r="H77" s="18" t="n"/>
+      <c r="I77" s="18" t="n"/>
+      <c r="J77" s="18" t="n"/>
+      <c r="K77" s="18" t="n"/>
+      <c r="L77" s="18" t="n"/>
+      <c r="M77" s="18" t="n"/>
+      <c r="N77" s="18" t="n"/>
+    </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Energy Revenue</t>
+          <t>Capacity Revenue</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -4388,24 +4599,24 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Generation × Power Price / 1M</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="inlineStr"/>
-      <c r="F78" s="18" t="inlineStr"/>
-      <c r="G78" s="18" t="inlineStr"/>
-      <c r="H78" s="18" t="inlineStr"/>
-      <c r="I78" s="18" t="inlineStr"/>
-      <c r="J78" s="18" t="inlineStr"/>
-      <c r="K78" s="18" t="inlineStr"/>
-      <c r="L78" s="18" t="inlineStr"/>
-      <c r="M78" s="18" t="inlineStr"/>
-      <c r="N78" s="18" t="inlineStr"/>
+          <t>UCAP × Cap Price × 1000 / 1M</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="n"/>
+      <c r="F78" s="18" t="n"/>
+      <c r="G78" s="18" t="n"/>
+      <c r="H78" s="18" t="n"/>
+      <c r="I78" s="18" t="n"/>
+      <c r="J78" s="18" t="n"/>
+      <c r="K78" s="18" t="n"/>
+      <c r="L78" s="18" t="n"/>
+      <c r="M78" s="18" t="n"/>
+      <c r="N78" s="18" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Capacity Revenue</t>
+          <t>Total Revenue</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -4413,147 +4624,151 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>UCAP × Cap Price × 1000 / 1M</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="inlineStr"/>
-      <c r="F79" s="18" t="inlineStr"/>
-      <c r="G79" s="18" t="inlineStr"/>
-      <c r="H79" s="18" t="inlineStr"/>
-      <c r="I79" s="18" t="inlineStr"/>
-      <c r="J79" s="18" t="inlineStr"/>
-      <c r="K79" s="18" t="inlineStr"/>
-      <c r="L79" s="18" t="inlineStr"/>
-      <c r="M79" s="18" t="inlineStr"/>
-      <c r="N79" s="18" t="inlineStr"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="E79" s="20" t="n"/>
+      <c r="F79" s="20" t="n"/>
+      <c r="G79" s="20" t="n"/>
+      <c r="H79" s="20" t="n"/>
+      <c r="I79" s="20" t="n"/>
+      <c r="J79" s="20" t="n"/>
+      <c r="K79" s="20" t="n"/>
+      <c r="L79" s="20" t="n"/>
+      <c r="M79" s="20" t="n"/>
+      <c r="N79" s="20" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr"/>
-      <c r="E80" s="20" t="inlineStr"/>
-      <c r="F80" s="20" t="inlineStr"/>
-      <c r="G80" s="20" t="inlineStr"/>
-      <c r="H80" s="20" t="inlineStr"/>
-      <c r="I80" s="20" t="inlineStr"/>
-      <c r="J80" s="20" t="inlineStr"/>
-      <c r="K80" s="20" t="inlineStr"/>
-      <c r="L80" s="20" t="inlineStr"/>
-      <c r="M80" s="20" t="inlineStr"/>
-      <c r="N80" s="20" t="inlineStr"/>
-    </row>
-    <row r="81"/>
+      <c r="A80" s="5" t="n"/>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="E80" s="20" t="n"/>
+      <c r="F80" s="20" t="n"/>
+      <c r="G80" s="20" t="n"/>
+      <c r="H80" s="20" t="n"/>
+      <c r="I80" s="20" t="n"/>
+      <c r="J80" s="20" t="n"/>
+      <c r="K80" s="20" t="n"/>
+      <c r="L80" s="20" t="n"/>
+      <c r="M80" s="20" t="n"/>
+      <c r="N80" s="20" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Fuel Cost</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Gen × HR × Gas / 1B</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="n"/>
+      <c r="F81" s="18" t="n"/>
+      <c r="G81" s="18" t="n"/>
+      <c r="H81" s="18" t="n"/>
+      <c r="I81" s="18" t="n"/>
+      <c r="J81" s="18" t="n"/>
+      <c r="K81" s="18" t="n"/>
+      <c r="L81" s="18" t="n"/>
+      <c r="M81" s="18" t="n"/>
+      <c r="N81" s="18" t="n"/>
+    </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Fuel Cost</t>
+      <c r="A82" s="34" t="inlineStr">
+        <is>
+          <t>Spark Spread</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Gen × HR × Gas / 1B</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="inlineStr"/>
-      <c r="F82" s="18" t="inlineStr"/>
-      <c r="G82" s="18" t="inlineStr"/>
-      <c r="H82" s="18" t="inlineStr"/>
-      <c r="I82" s="18" t="inlineStr"/>
-      <c r="J82" s="18" t="inlineStr"/>
-      <c r="K82" s="18" t="inlineStr"/>
-      <c r="L82" s="18" t="inlineStr"/>
-      <c r="M82" s="18" t="inlineStr"/>
-      <c r="N82" s="18" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="34" t="inlineStr">
-        <is>
-          <t>Spark Spread</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
           <t>$/MWh</t>
         </is>
       </c>
-      <c r="C83" s="55" t="inlineStr">
+      <c r="C82" s="55" t="inlineStr">
         <is>
           <t>[WHAT] Spark Spread = Power Price - (Plant HR × Gas / 1000)
 [WHY] Gross margin per MWh after fuel. Core driver of thermal profitability.
 [RMHR EQUIVALENCE - For Interview Discussion]
-Traders express this as "Market Heat Rate":
-  RMHR = Power / Gas × 1000
-  If RMHR &gt; Plant HR → "In the money" → Dispatch
-Spark Spread = (RMHR - Plant HR) × Gas / 1000
-Same math, different framing. Use Spark Spread in model (simpler).
-[EXAMPLE] Power=$50, Gas=$5, HR=7000
-  RMHR = 50/5 × 1000 = 10,000 Btu/kWh
-  Spread = 10,000 - 7,000 = 3,000 Btu/kWh
-  Spark = 3,000 × $5 / 1000 = $15/MWh ✓
-  (Or directly: $50 - 7×$5 = $15/MWh)
-[UNITS] $/MWh - (Btu/kWh × $/MMBtu / 1000) = $/MWh ✓</t>
-        </is>
-      </c>
-      <c r="E83" s="56">
-        <f>E72-($D$34/1000)*E74</f>
-        <v/>
-      </c>
-      <c r="F83" s="56">
-        <f>F72-($D$34/1000)*F74</f>
-        <v/>
-      </c>
-      <c r="G83" s="56">
-        <f>G72-($D$34/1000)*G74</f>
-        <v/>
-      </c>
-      <c r="H83" s="56">
-        <f>H72-($D$34/1000)*H74</f>
-        <v/>
-      </c>
-      <c r="I83" s="56">
-        <f>I72-($D$34/1000)*I74</f>
-        <v/>
-      </c>
-      <c r="J83" s="56">
-        <f>J72-($D$34/1000)*J74</f>
-        <v/>
-      </c>
-      <c r="K83" s="56">
-        <f>K72-($D$34/1000)*K74</f>
-        <v/>
-      </c>
-      <c r="L83" s="56">
-        <f>L72-($D$34/1000)*L74</f>
-        <v/>
-      </c>
-      <c r="M83" s="56">
-        <f>M72-($D$34/1000)*M74</f>
-        <v/>
-      </c>
-      <c r="N83" s="56">
-        <f>N72-($D$34/1000)*N74</f>
-        <v/>
-      </c>
+Traders express this as "Market Heat Rate":</t>
+        </is>
+      </c>
+      <c r="E82" s="56">
+        <f>E73-($D$35/1000)*E75</f>
+        <v/>
+      </c>
+      <c r="F82" s="56">
+        <f>F73-($D$35/1000)*F75</f>
+        <v/>
+      </c>
+      <c r="G82" s="56">
+        <f>G73-($D$35/1000)*G75</f>
+        <v/>
+      </c>
+      <c r="H82" s="56">
+        <f>H73-($D$35/1000)*H75</f>
+        <v/>
+      </c>
+      <c r="I82" s="56">
+        <f>I73-($D$35/1000)*I75</f>
+        <v/>
+      </c>
+      <c r="J82" s="56">
+        <f>J73-($D$35/1000)*J75</f>
+        <v/>
+      </c>
+      <c r="K82" s="56">
+        <f>K73-($D$35/1000)*K75</f>
+        <v/>
+      </c>
+      <c r="L82" s="56">
+        <f>L73-($D$35/1000)*L75</f>
+        <v/>
+      </c>
+      <c r="M82" s="56">
+        <f>M73-($D$35/1000)*M75</f>
+        <v/>
+      </c>
+      <c r="N82" s="56">
+        <f>N73-($D$35/1000)*N75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>VOM</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Generation × VOM rate / 1M</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="n"/>
+      <c r="F83" s="18" t="n"/>
+      <c r="G83" s="18" t="n"/>
+      <c r="H83" s="18" t="n"/>
+      <c r="I83" s="18" t="n"/>
+      <c r="J83" s="18" t="n"/>
+      <c r="K83" s="18" t="n"/>
+      <c r="L83" s="18" t="n"/>
+      <c r="M83" s="18" t="n"/>
+      <c r="N83" s="18" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>VOM</t>
+          <t>FOM</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -4563,54 +4778,24 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Generation × VOM rate / 1M</t>
-        </is>
-      </c>
-      <c r="E84" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="F84" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="G84" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="H84" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="I84" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="J84" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="K84" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="L84" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="M84" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
-      <c r="N84" s="18">
-        <f>$D$56*$D$36/1000000</f>
-        <v/>
-      </c>
+          <t>Capacity × FOM × esc × 1000 / 1M</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="n"/>
+      <c r="F84" s="18" t="n"/>
+      <c r="G84" s="18" t="n"/>
+      <c r="H84" s="18" t="n"/>
+      <c r="I84" s="18" t="n"/>
+      <c r="J84" s="18" t="n"/>
+      <c r="K84" s="18" t="n"/>
+      <c r="L84" s="18" t="n"/>
+      <c r="M84" s="18" t="n"/>
+      <c r="N84" s="18" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>FOM</t>
+          <t>Total Operating Costs</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -4618,154 +4803,157 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>Capacity × FOM × esc × 1000 / 1M</t>
-        </is>
-      </c>
-      <c r="E85" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(1-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="F85" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(2-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="G85" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(3-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="H85" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(4-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="I85" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(5-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="J85" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(6-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="K85" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(7-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="L85" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(8-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="M85" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(9-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="N85" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(10-1)*1000/1000000</f>
-        <v/>
-      </c>
+      <c r="C85" s="6" t="n"/>
+      <c r="E85" s="18" t="n"/>
+      <c r="F85" s="18" t="n"/>
+      <c r="G85" s="18" t="n"/>
+      <c r="H85" s="18" t="n"/>
+      <c r="I85" s="18" t="n"/>
+      <c r="J85" s="18" t="n"/>
+      <c r="K85" s="18" t="n"/>
+      <c r="L85" s="18" t="n"/>
+      <c r="M85" s="18" t="n"/>
+      <c r="N85" s="18" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>Total Operating Costs</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr"/>
-      <c r="E86" s="18">
-        <f>E70+E71+E72</f>
-        <v/>
-      </c>
-      <c r="F86" s="18">
-        <f>F70+F71+F72</f>
-        <v/>
-      </c>
-      <c r="G86" s="18">
-        <f>G70+G71+G72</f>
-        <v/>
-      </c>
-      <c r="H86" s="18">
-        <f>H70+H71+H72</f>
-        <v/>
-      </c>
-      <c r="I86" s="18">
-        <f>I70+I71+I72</f>
-        <v/>
-      </c>
-      <c r="J86" s="18">
-        <f>J70+J71+J72</f>
-        <v/>
-      </c>
-      <c r="K86" s="18">
-        <f>K70+K71+K72</f>
-        <v/>
-      </c>
-      <c r="L86" s="18">
-        <f>L70+L71+L72</f>
-        <v/>
-      </c>
-      <c r="M86" s="18">
-        <f>M70+M71+M72</f>
-        <v/>
-      </c>
-      <c r="N86" s="18">
-        <f>N70+N71+N72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87"/>
+      <c r="A86" s="5" t="n"/>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="E86" s="18" t="n"/>
+      <c r="F86" s="18" t="n"/>
+      <c r="G86" s="18" t="n"/>
+      <c r="H86" s="18" t="n"/>
+      <c r="I86" s="18" t="n"/>
+      <c r="J86" s="18" t="n"/>
+      <c r="K86" s="18" t="n"/>
+      <c r="L86" s="18" t="n"/>
+      <c r="M86" s="18" t="n"/>
+      <c r="N86" s="18" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="7" t="n"/>
+      <c r="G87" s="7" t="n"/>
+      <c r="H87" s="7" t="n"/>
+      <c r="I87" s="7" t="n"/>
+      <c r="J87" s="7" t="n"/>
+      <c r="K87" s="7" t="n"/>
+      <c r="L87" s="7" t="n"/>
+      <c r="M87" s="7" t="n"/>
+      <c r="N87" s="7" t="n"/>
+    </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr"/>
-      <c r="E88" s="7" t="inlineStr"/>
-      <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="7" t="inlineStr"/>
-      <c r="J88" s="7" t="inlineStr"/>
-      <c r="K88" s="7" t="inlineStr"/>
-      <c r="L88" s="7" t="inlineStr"/>
-      <c r="M88" s="7" t="inlineStr"/>
-      <c r="N88" s="7" t="inlineStr"/>
-    </row>
-    <row r="89"/>
+      <c r="A88" s="5" t="n"/>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="E88" s="7" t="n"/>
+      <c r="F88" s="7" t="n"/>
+      <c r="G88" s="7" t="n"/>
+      <c r="H88" s="7" t="n"/>
+      <c r="I88" s="7" t="n"/>
+      <c r="J88" s="7" t="n"/>
+      <c r="K88" s="7" t="n"/>
+      <c r="L88" s="7" t="n"/>
+      <c r="M88" s="7" t="n"/>
+      <c r="N88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>CASH FLOW</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+      <c r="G89" s="4" t="n"/>
+      <c r="H89" s="4" t="n"/>
+      <c r="I89" s="4" t="n"/>
+      <c r="J89" s="4" t="n"/>
+      <c r="K89" s="4" t="n"/>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
+      <c r="N89" s="4" t="n"/>
+    </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>CASH FLOW</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n"/>
-      <c r="C90" s="4" t="n"/>
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA - Depreciation</t>
+        </is>
+      </c>
       <c r="D90" s="4" t="n"/>
-      <c r="E90" s="4" t="n"/>
-      <c r="F90" s="4" t="n"/>
-      <c r="G90" s="4" t="n"/>
-      <c r="H90" s="4" t="n"/>
-      <c r="I90" s="4" t="n"/>
-      <c r="J90" s="4" t="n"/>
-      <c r="K90" s="4" t="n"/>
-      <c r="L90" s="4" t="n"/>
-      <c r="M90" s="4" t="n"/>
-      <c r="N90" s="4" t="n"/>
+      <c r="E90" s="18">
+        <f>E87-$D$69</f>
+        <v/>
+      </c>
+      <c r="F90" s="18">
+        <f>F87-$D$69</f>
+        <v/>
+      </c>
+      <c r="G90" s="18">
+        <f>G87-$D$69</f>
+        <v/>
+      </c>
+      <c r="H90" s="18">
+        <f>H87-$D$69</f>
+        <v/>
+      </c>
+      <c r="I90" s="18">
+        <f>I87-$D$69</f>
+        <v/>
+      </c>
+      <c r="J90" s="18">
+        <f>J87-$D$69</f>
+        <v/>
+      </c>
+      <c r="K90" s="18">
+        <f>K87-$D$69</f>
+        <v/>
+      </c>
+      <c r="L90" s="18">
+        <f>L87-$D$69</f>
+        <v/>
+      </c>
+      <c r="M90" s="18">
+        <f>M87-$D$69</f>
+        <v/>
+      </c>
+      <c r="N90" s="18">
+        <f>N87-$D$69</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -4775,24 +4963,24 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>EBITDA - Depreciation</t>
-        </is>
-      </c>
-      <c r="E91" s="18" t="inlineStr"/>
-      <c r="F91" s="18" t="inlineStr"/>
-      <c r="G91" s="18" t="inlineStr"/>
-      <c r="H91" s="18" t="inlineStr"/>
-      <c r="I91" s="18" t="inlineStr"/>
-      <c r="J91" s="18" t="inlineStr"/>
-      <c r="K91" s="18" t="inlineStr"/>
-      <c r="L91" s="18" t="inlineStr"/>
-      <c r="M91" s="18" t="inlineStr"/>
-      <c r="N91" s="18" t="inlineStr"/>
+          <t>MAX(0, EBIT) × Tax Rate</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="n"/>
+      <c r="F91" s="18" t="n"/>
+      <c r="G91" s="18" t="n"/>
+      <c r="H91" s="18" t="n"/>
+      <c r="I91" s="18" t="n"/>
+      <c r="J91" s="18" t="n"/>
+      <c r="K91" s="18" t="n"/>
+      <c r="L91" s="18" t="n"/>
+      <c r="M91" s="18" t="n"/>
+      <c r="N91" s="18" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Major Maintenance</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -4802,24 +4990,24 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, EBIT) × Tax Rate</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="inlineStr"/>
-      <c r="F92" s="18" t="inlineStr"/>
-      <c r="G92" s="18" t="inlineStr"/>
-      <c r="H92" s="18" t="inlineStr"/>
-      <c r="I92" s="18" t="inlineStr"/>
-      <c r="J92" s="18" t="inlineStr"/>
-      <c r="K92" s="18" t="inlineStr"/>
-      <c r="L92" s="18" t="inlineStr"/>
-      <c r="M92" s="18" t="inlineStr"/>
-      <c r="N92" s="18" t="inlineStr"/>
+          <t>HGP in specified year</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="n"/>
+      <c r="F92" s="21" t="n"/>
+      <c r="G92" s="21" t="n"/>
+      <c r="H92" s="21" t="n"/>
+      <c r="I92" s="21" t="n"/>
+      <c r="J92" s="21" t="n"/>
+      <c r="K92" s="21" t="n"/>
+      <c r="L92" s="21" t="n"/>
+      <c r="M92" s="21" t="n"/>
+      <c r="N92" s="21" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Major Maintenance</t>
+          <t>CFADS</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -4829,102 +5017,119 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>HGP in specified year</t>
-        </is>
-      </c>
-      <c r="E93" s="21">
-        <f>IF(1=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="F93" s="21">
-        <f>IF(2=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="G93" s="21">
-        <f>IF(3=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="H93" s="21">
-        <f>IF(4=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="I93" s="21">
-        <f>IF(5=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="J93" s="21">
-        <f>IF(6=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="K93" s="21">
-        <f>IF(7=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="L93" s="21">
-        <f>IF(8=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="M93" s="21">
-        <f>IF(9=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
-      <c r="N93" s="21">
-        <f>IF(10=$D$38,$D$39,0)</f>
-        <v/>
-      </c>
+          <t>EBITDA - Taxes - Maint</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="n"/>
+      <c r="F93" s="7" t="n"/>
+      <c r="G93" s="7" t="n"/>
+      <c r="H93" s="7" t="n"/>
+      <c r="I93" s="7" t="n"/>
+      <c r="J93" s="7" t="n"/>
+      <c r="K93" s="7" t="n"/>
+      <c r="L93" s="7" t="n"/>
+      <c r="M93" s="7" t="n"/>
+      <c r="N93" s="7" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>CFADS</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA - Taxes - Maint</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr"/>
-      <c r="F94" s="7" t="inlineStr"/>
-      <c r="G94" s="7" t="inlineStr"/>
-      <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr"/>
-      <c r="J94" s="7" t="inlineStr"/>
-      <c r="K94" s="7" t="inlineStr"/>
-      <c r="L94" s="7" t="inlineStr"/>
-      <c r="M94" s="7" t="inlineStr"/>
-      <c r="N94" s="7" t="inlineStr"/>
-    </row>
-    <row r="95"/>
+      <c r="A94" s="5" t="n"/>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="E94" s="7" t="n"/>
+      <c r="F94" s="7" t="n"/>
+      <c r="G94" s="7" t="n"/>
+      <c r="H94" s="7" t="n"/>
+      <c r="I94" s="7" t="n"/>
+      <c r="J94" s="7" t="n"/>
+      <c r="K94" s="7" t="n"/>
+      <c r="L94" s="7" t="n"/>
+      <c r="M94" s="7" t="n"/>
+      <c r="N94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>DEBT SCHEDULE (50% Cash Sweep)</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>MIN(Excess×%, Bal−Sched)</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="n"/>
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n"/>
+      <c r="I95" s="4" t="n"/>
+      <c r="J95" s="4" t="n"/>
+      <c r="K95" s="4" t="n"/>
+      <c r="L95" s="4" t="n"/>
+      <c r="M95" s="4" t="n"/>
+      <c r="N95" s="4" t="n"/>
+    </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>DEBT SCHEDULE (50% Cash Sweep)</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="n"/>
-      <c r="C96" s="4" t="n"/>
-      <c r="D96" s="4" t="n"/>
-      <c r="E96" s="4" t="n"/>
-      <c r="F96" s="4" t="n"/>
-      <c r="G96" s="4" t="n"/>
-      <c r="H96" s="4" t="n"/>
-      <c r="I96" s="4" t="n"/>
-      <c r="J96" s="4" t="n"/>
-      <c r="K96" s="4" t="n"/>
-      <c r="L96" s="4" t="n"/>
-      <c r="M96" s="4" t="n"/>
-      <c r="N96" s="4" t="n"/>
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="18">
+        <f>$D$68</f>
+        <v/>
+      </c>
+      <c r="F96" s="18">
+        <f>E103</f>
+        <v/>
+      </c>
+      <c r="G96" s="18">
+        <f>F103</f>
+        <v/>
+      </c>
+      <c r="H96" s="18">
+        <f>G103</f>
+        <v/>
+      </c>
+      <c r="I96" s="18">
+        <f>H103</f>
+        <v/>
+      </c>
+      <c r="J96" s="18">
+        <f>I103</f>
+        <v/>
+      </c>
+      <c r="K96" s="18">
+        <f>J103</f>
+        <v/>
+      </c>
+      <c r="L96" s="18">
+        <f>K103</f>
+        <v/>
+      </c>
+      <c r="M96" s="18">
+        <f>L103</f>
+        <v/>
+      </c>
+      <c r="N96" s="18">
+        <f>M103</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Beginning Balance</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -4932,52 +5137,26 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr"/>
-      <c r="E97" s="18">
-        <f>$D$57</f>
-        <v/>
-      </c>
-      <c r="F97" s="18">
-        <f>E91</f>
-        <v/>
-      </c>
-      <c r="G97" s="18">
-        <f>F91</f>
-        <v/>
-      </c>
-      <c r="H97" s="18">
-        <f>G91</f>
-        <v/>
-      </c>
-      <c r="I97" s="18">
-        <f>H91</f>
-        <v/>
-      </c>
-      <c r="J97" s="18">
-        <f>I91</f>
-        <v/>
-      </c>
-      <c r="K97" s="18">
-        <f>J91</f>
-        <v/>
-      </c>
-      <c r="L97" s="18">
-        <f>K91</f>
-        <v/>
-      </c>
-      <c r="M97" s="18">
-        <f>L91</f>
-        <v/>
-      </c>
-      <c r="N97" s="18">
-        <f>M91</f>
-        <v/>
-      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Beg Bal × Int Rate</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n"/>
+      <c r="F97" s="18" t="n"/>
+      <c r="G97" s="18" t="n"/>
+      <c r="H97" s="18" t="n"/>
+      <c r="I97" s="18" t="n"/>
+      <c r="J97" s="18" t="n"/>
+      <c r="K97" s="18" t="n"/>
+      <c r="L97" s="18" t="n"/>
+      <c r="M97" s="18" t="n"/>
+      <c r="N97" s="18" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Scheduled Principal</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -4987,24 +5166,24 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>Beg Bal × Int Rate</t>
-        </is>
-      </c>
-      <c r="E98" s="18" t="inlineStr"/>
-      <c r="F98" s="18" t="inlineStr"/>
-      <c r="G98" s="18" t="inlineStr"/>
-      <c r="H98" s="18" t="inlineStr"/>
-      <c r="I98" s="18" t="inlineStr"/>
-      <c r="J98" s="18" t="inlineStr"/>
-      <c r="K98" s="18" t="inlineStr"/>
-      <c r="L98" s="18" t="inlineStr"/>
-      <c r="M98" s="18" t="inlineStr"/>
-      <c r="N98" s="18" t="inlineStr"/>
+          <t>MIN(Sched, Beg Bal)</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n"/>
+      <c r="F98" s="18" t="n"/>
+      <c r="G98" s="18" t="n"/>
+      <c r="H98" s="18" t="n"/>
+      <c r="I98" s="18" t="n"/>
+      <c r="J98" s="18" t="n"/>
+      <c r="K98" s="18" t="n"/>
+      <c r="L98" s="18" t="n"/>
+      <c r="M98" s="18" t="n"/>
+      <c r="N98" s="18" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Scheduled Principal</t>
+          <t>Debt Service (Pre-Sweep)</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -5014,24 +5193,24 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>MIN(Sched, Beg Bal)</t>
-        </is>
-      </c>
-      <c r="E99" s="18" t="inlineStr"/>
-      <c r="F99" s="18" t="inlineStr"/>
-      <c r="G99" s="18" t="inlineStr"/>
-      <c r="H99" s="18" t="inlineStr"/>
-      <c r="I99" s="18" t="inlineStr"/>
-      <c r="J99" s="18" t="inlineStr"/>
-      <c r="K99" s="18" t="inlineStr"/>
-      <c r="L99" s="18" t="inlineStr"/>
-      <c r="M99" s="18" t="inlineStr"/>
-      <c r="N99" s="18" t="inlineStr"/>
+          <t>Interest + Sched Prin</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n"/>
+      <c r="F99" s="18" t="n"/>
+      <c r="G99" s="18" t="n"/>
+      <c r="H99" s="18" t="n"/>
+      <c r="I99" s="18" t="n"/>
+      <c r="J99" s="18" t="n"/>
+      <c r="K99" s="18" t="n"/>
+      <c r="L99" s="18" t="n"/>
+      <c r="M99" s="18" t="n"/>
+      <c r="N99" s="18" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Debt Service (Pre-Sweep)</t>
+          <t>Excess Cash</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -5041,54 +5220,54 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Interest + Sched Prin</t>
+          <t>CFADS - DS - DSRA Funding</t>
         </is>
       </c>
       <c r="E100" s="18">
-        <f>E85+E86</f>
+        <f>MAX(0,E93-E99-E109)</f>
         <v/>
       </c>
       <c r="F100" s="18">
-        <f>F85+F86</f>
+        <f>MAX(0,F93-F99-F109)</f>
         <v/>
       </c>
       <c r="G100" s="18">
-        <f>G85+G86</f>
+        <f>MAX(0,G93-G99-G109)</f>
         <v/>
       </c>
       <c r="H100" s="18">
-        <f>H85+H86</f>
+        <f>MAX(0,H93-H99-H109)</f>
         <v/>
       </c>
       <c r="I100" s="18">
-        <f>I85+I86</f>
+        <f>MAX(0,I93-I99-I109)</f>
         <v/>
       </c>
       <c r="J100" s="18">
-        <f>J85+J86</f>
+        <f>MAX(0,J93-J99-J109)</f>
         <v/>
       </c>
       <c r="K100" s="18">
-        <f>K85+K86</f>
+        <f>MAX(0,K93-K99-K109)</f>
         <v/>
       </c>
       <c r="L100" s="18">
-        <f>L85+L86</f>
+        <f>MAX(0,L93-L99-L109)</f>
         <v/>
       </c>
       <c r="M100" s="18">
-        <f>M85+M86</f>
+        <f>MAX(0,M93-M99-M109)</f>
         <v/>
       </c>
       <c r="N100" s="18">
-        <f>N85+N86</f>
+        <f>MAX(0,N93-N99-N109)</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Excess Cash</t>
+          <t>Cash Sweep</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -5098,54 +5277,24 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>CFADS - DS - DSRA Funding</t>
-        </is>
-      </c>
-      <c r="E101" s="18">
-        <f>MAX(0,E81-E87-E97)</f>
-        <v/>
-      </c>
-      <c r="F101" s="18">
-        <f>MAX(0,F81-F87-F97)</f>
-        <v/>
-      </c>
-      <c r="G101" s="18">
-        <f>MAX(0,G81-G87-G97)</f>
-        <v/>
-      </c>
-      <c r="H101" s="18">
-        <f>MAX(0,H81-H87-H97)</f>
-        <v/>
-      </c>
-      <c r="I101" s="18">
-        <f>MAX(0,I81-I87-I97)</f>
-        <v/>
-      </c>
-      <c r="J101" s="18">
-        <f>MAX(0,J81-J87-J97)</f>
-        <v/>
-      </c>
-      <c r="K101" s="18">
-        <f>MAX(0,K81-K87-K97)</f>
-        <v/>
-      </c>
-      <c r="L101" s="18">
-        <f>MAX(0,L81-L87-L97)</f>
-        <v/>
-      </c>
-      <c r="M101" s="18">
-        <f>MAX(0,M81-M87-M97)</f>
-        <v/>
-      </c>
-      <c r="N101" s="18">
-        <f>MAX(0,N81-N87-N97)</f>
-        <v/>
-      </c>
+          <t>MIN(Excess×50%, Beg-Sched)</t>
+        </is>
+      </c>
+      <c r="E101" s="21" t="n"/>
+      <c r="F101" s="21" t="n"/>
+      <c r="G101" s="21" t="n"/>
+      <c r="H101" s="21" t="n"/>
+      <c r="I101" s="21" t="n"/>
+      <c r="J101" s="21" t="n"/>
+      <c r="K101" s="21" t="n"/>
+      <c r="L101" s="21" t="n"/>
+      <c r="M101" s="21" t="n"/>
+      <c r="N101" s="21" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep</t>
+          <t>Total Principal</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
@@ -5155,24 +5304,24 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>MIN(Excess×50%, Beg-Sched)</t>
-        </is>
-      </c>
-      <c r="E102" s="21" t="inlineStr"/>
-      <c r="F102" s="21" t="inlineStr"/>
-      <c r="G102" s="21" t="inlineStr"/>
-      <c r="H102" s="21" t="inlineStr"/>
-      <c r="I102" s="21" t="inlineStr"/>
-      <c r="J102" s="21" t="inlineStr"/>
-      <c r="K102" s="21" t="inlineStr"/>
-      <c r="L102" s="21" t="inlineStr"/>
-      <c r="M102" s="21" t="inlineStr"/>
-      <c r="N102" s="21" t="inlineStr"/>
+          <t>Scheduled + Sweep</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n"/>
+      <c r="F102" s="18" t="n"/>
+      <c r="G102" s="18" t="n"/>
+      <c r="H102" s="18" t="n"/>
+      <c r="I102" s="18" t="n"/>
+      <c r="J102" s="18" t="n"/>
+      <c r="K102" s="18" t="n"/>
+      <c r="L102" s="18" t="n"/>
+      <c r="M102" s="18" t="n"/>
+      <c r="N102" s="18" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Total Principal</t>
+          <t>Ending Balance</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -5182,155 +5331,192 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Scheduled + Sweep</t>
-        </is>
-      </c>
-      <c r="E103" s="18" t="inlineStr"/>
-      <c r="F103" s="18" t="inlineStr"/>
-      <c r="G103" s="18" t="inlineStr"/>
-      <c r="H103" s="18" t="inlineStr"/>
-      <c r="I103" s="18" t="inlineStr"/>
-      <c r="J103" s="18" t="inlineStr"/>
-      <c r="K103" s="18" t="inlineStr"/>
-      <c r="L103" s="18" t="inlineStr"/>
-      <c r="M103" s="18" t="inlineStr"/>
-      <c r="N103" s="18" t="inlineStr"/>
+          <t>MAX(0, Beg - Total Prin)</t>
+        </is>
+      </c>
+      <c r="D103">
+        <f>$D$68</f>
+        <v/>
+      </c>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="18" t="n"/>
+      <c r="G103" s="18" t="n"/>
+      <c r="H103" s="18" t="n"/>
+      <c r="I103" s="18" t="n"/>
+      <c r="J103" s="18" t="n"/>
+      <c r="K103" s="18" t="n"/>
+      <c r="L103" s="18" t="n"/>
+      <c r="M103" s="18" t="n"/>
+      <c r="N103" s="18" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Ending Balance</t>
+          <t>DSCR</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, Beg - Total Prin)</t>
-        </is>
-      </c>
-      <c r="E104" s="18" t="inlineStr"/>
-      <c r="F104" s="18" t="inlineStr"/>
-      <c r="G104" s="18" t="inlineStr"/>
-      <c r="H104" s="18" t="inlineStr"/>
-      <c r="I104" s="18" t="inlineStr"/>
-      <c r="J104" s="18" t="inlineStr"/>
-      <c r="K104" s="18" t="inlineStr"/>
-      <c r="L104" s="18" t="inlineStr"/>
-      <c r="M104" s="18" t="inlineStr"/>
-      <c r="N104" s="18" t="inlineStr"/>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
+      <c r="E104" s="30" t="n"/>
+      <c r="F104" s="30" t="n"/>
+      <c r="G104" s="30" t="n"/>
+      <c r="H104" s="30" t="n"/>
+      <c r="I104" s="30" t="n"/>
+      <c r="J104" s="30" t="n"/>
+      <c r="K104" s="30" t="n"/>
+      <c r="L104" s="30" t="n"/>
+      <c r="M104" s="30" t="n"/>
+      <c r="N104" s="30" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>DSCR</t>
+          <t>Scheduled DS (for DSRA)</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="E105" s="30" t="inlineStr"/>
-      <c r="F105" s="30" t="inlineStr"/>
-      <c r="G105" s="30" t="inlineStr"/>
-      <c r="H105" s="30" t="inlineStr"/>
-      <c r="I105" s="30" t="inlineStr"/>
-      <c r="J105" s="30" t="inlineStr"/>
-      <c r="K105" s="30" t="inlineStr"/>
-      <c r="L105" s="30" t="inlineStr"/>
-      <c r="M105" s="30" t="inlineStr"/>
-      <c r="N105" s="30" t="inlineStr"/>
+          <t>Based on straight-line amort</t>
+        </is>
+      </c>
+      <c r="E105" s="18">
+        <f>MAX(0,$D$68-(1-1)*$D$70)*$D$54+$D$70</f>
+        <v/>
+      </c>
+      <c r="F105" s="18">
+        <f>MAX(0,$D$68-(2-1)*$D$70)*$D$54+$D$70</f>
+        <v/>
+      </c>
+      <c r="G105" s="18">
+        <f>MAX(0,$D$68-(3-1)*$D$70)*$D$54+$D$70</f>
+        <v/>
+      </c>
+      <c r="H105" s="18">
+        <f>MAX(0,$D$68-(4-1)*$D$70)*$D$54+$D$70</f>
+        <v/>
+      </c>
+      <c r="I105" s="18">
+        <f>MAX(0,$D$68-(5-1)*$D$70)*$D$54+$D$70</f>
+        <v/>
+      </c>
+      <c r="J105" s="18">
+        <f>MAX(0,$D$68-(6-1)*$D$70)*$D$54+$D$70</f>
+        <v/>
+      </c>
+      <c r="K105" s="18">
+        <f>MAX(0,$D$68-(7-1)*$D$70)*$D$54+$D$70</f>
+        <v/>
+      </c>
+      <c r="L105" s="18">
+        <f>MAX(0,$D$68-(8-1)*$D$70)*$D$54+$D$70</f>
+        <v/>
+      </c>
+      <c r="M105" s="18">
+        <f>MAX(0,$D$68-(9-1)*$D$70)*$D$54+$D$70</f>
+        <v/>
+      </c>
+      <c r="N105" s="18">
+        <f>MAX(0,$D$68-(10-1)*$D$70)*$D$54+$D$70</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Scheduled DS (for DSRA)</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>Based on straight-line amort</t>
-        </is>
-      </c>
-      <c r="E106" s="18">
-        <f>MAX(0,$D$57-(1-1)*$D$59)*$D$43+$D$59</f>
-        <v/>
-      </c>
-      <c r="F106" s="18">
-        <f>MAX(0,$D$57-(2-1)*$D$59)*$D$43+$D$59</f>
-        <v/>
-      </c>
-      <c r="G106" s="18">
-        <f>MAX(0,$D$57-(3-1)*$D$59)*$D$43+$D$59</f>
-        <v/>
-      </c>
-      <c r="H106" s="18">
-        <f>MAX(0,$D$57-(4-1)*$D$59)*$D$43+$D$59</f>
-        <v/>
-      </c>
-      <c r="I106" s="18">
-        <f>MAX(0,$D$57-(5-1)*$D$59)*$D$43+$D$59</f>
-        <v/>
-      </c>
-      <c r="J106" s="18">
-        <f>MAX(0,$D$57-(6-1)*$D$59)*$D$43+$D$59</f>
-        <v/>
-      </c>
-      <c r="K106" s="18">
-        <f>MAX(0,$D$57-(7-1)*$D$59)*$D$43+$D$59</f>
-        <v/>
-      </c>
-      <c r="L106" s="18">
-        <f>MAX(0,$D$57-(8-1)*$D$59)*$D$43+$D$59</f>
-        <v/>
-      </c>
-      <c r="M106" s="18">
-        <f>MAX(0,$D$57-(9-1)*$D$59)*$D$43+$D$59</f>
-        <v/>
-      </c>
-      <c r="N106" s="18">
-        <f>MAX(0,$D$57-(10-1)*$D$59)*$D$43+$D$59</f>
-        <v/>
-      </c>
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>DSRA (Debt Service Reserve Account)</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="4" t="n"/>
+      <c r="E106" s="4" t="n"/>
+      <c r="F106" s="4" t="n"/>
+      <c r="G106" s="4" t="n"/>
+      <c r="H106" s="4" t="n"/>
+      <c r="I106" s="4" t="n"/>
+      <c r="J106" s="4" t="n"/>
+      <c r="K106" s="4" t="n"/>
+      <c r="L106" s="4" t="n"/>
+      <c r="M106" s="4" t="n"/>
+      <c r="N106" s="4" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>DSRA (Debt Service Reserve Account)</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="n"/>
-      <c r="C107" s="4" t="n"/>
-      <c r="D107" s="4" t="n"/>
-      <c r="E107" s="4" t="n"/>
-      <c r="F107" s="4" t="n"/>
-      <c r="G107" s="4" t="n"/>
-      <c r="H107" s="4" t="n"/>
-      <c r="I107" s="4" t="n"/>
-      <c r="J107" s="4" t="n"/>
-      <c r="K107" s="4" t="n"/>
-      <c r="L107" s="4" t="n"/>
-      <c r="M107" s="4" t="n"/>
-      <c r="N107" s="4" t="n"/>
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>DSRA Target</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
+        </is>
+      </c>
+      <c r="D107" s="18">
+        <f>E93*$D$45/12</f>
+        <v/>
+      </c>
+      <c r="E107" s="18">
+        <f>F105*$D$56/12</f>
+        <v/>
+      </c>
+      <c r="F107" s="18">
+        <f>G105*$D$56/12</f>
+        <v/>
+      </c>
+      <c r="G107" s="18">
+        <f>H105*$D$56/12</f>
+        <v/>
+      </c>
+      <c r="H107" s="18">
+        <f>I105*$D$56/12</f>
+        <v/>
+      </c>
+      <c r="I107" s="18">
+        <f>J105*$D$56/12</f>
+        <v/>
+      </c>
+      <c r="J107" s="18">
+        <f>K105*$D$56/12</f>
+        <v/>
+      </c>
+      <c r="K107" s="18">
+        <f>L105*$D$56/12</f>
+        <v/>
+      </c>
+      <c r="L107" s="18">
+        <f>M105*$D$56/12</f>
+        <v/>
+      </c>
+      <c r="M107" s="18">
+        <f>N105*$D$56/12</f>
+        <v/>
+      </c>
+      <c r="N107" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>DSRA Target</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
@@ -5338,60 +5524,55 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
-        </is>
-      </c>
-      <c r="D108" s="18">
-        <f>E93*$D$45/12</f>
-        <v/>
+      <c r="C108" s="6" t="n"/>
+      <c r="D108" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="E108" s="18">
-        <f>F93*$D$45/12</f>
+        <f>D121</f>
         <v/>
       </c>
       <c r="F108" s="18">
-        <f>G93*$D$45/12</f>
+        <f>E110</f>
         <v/>
       </c>
       <c r="G108" s="18">
-        <f>H93*$D$45/12</f>
+        <f>F110</f>
         <v/>
       </c>
       <c r="H108" s="18">
-        <f>I93*$D$45/12</f>
+        <f>G110</f>
         <v/>
       </c>
       <c r="I108" s="18">
-        <f>J93*$D$45/12</f>
+        <f>H110</f>
         <v/>
       </c>
       <c r="J108" s="18">
-        <f>K93*$D$45/12</f>
+        <f>I110</f>
         <v/>
       </c>
       <c r="K108" s="18">
-        <f>L93*$D$45/12</f>
+        <f>J110</f>
         <v/>
       </c>
       <c r="L108" s="18">
-        <f>M93*$D$45/12</f>
+        <f>K110</f>
         <v/>
       </c>
       <c r="M108" s="18">
-        <f>N93*$D$45/12</f>
+        <f>L110</f>
         <v/>
       </c>
       <c r="N108" s="18">
-        <f>0</f>
+        <f>M110</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Funding/(Release)</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -5399,56 +5580,60 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr"/>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
       <c r="D109" s="18">
-        <f>0</f>
+        <f>D95-D96</f>
         <v/>
       </c>
       <c r="E109" s="18">
-        <f>D98</f>
+        <f>E107-E108</f>
         <v/>
       </c>
       <c r="F109" s="18">
-        <f>E98</f>
+        <f>F107-F108</f>
         <v/>
       </c>
       <c r="G109" s="18">
-        <f>F98</f>
+        <f>G107-G108</f>
         <v/>
       </c>
       <c r="H109" s="18">
-        <f>G98</f>
+        <f>H107-H108</f>
         <v/>
       </c>
       <c r="I109" s="18">
-        <f>H98</f>
+        <f>I107-I108</f>
         <v/>
       </c>
       <c r="J109" s="18">
-        <f>I98</f>
+        <f>J107-J108</f>
         <v/>
       </c>
       <c r="K109" s="18">
-        <f>J98</f>
+        <f>K107-K108</f>
         <v/>
       </c>
       <c r="L109" s="18">
-        <f>K98</f>
+        <f>L107-L108</f>
         <v/>
       </c>
       <c r="M109" s="18">
-        <f>L98</f>
+        <f>M107-M108</f>
         <v/>
       </c>
       <c r="N109" s="18">
-        <f>M98</f>
+        <f>N107-N108</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Ending</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
@@ -5458,282 +5643,301 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>Target - Beginning</t>
+          <t>Beginning + Funding</t>
         </is>
       </c>
       <c r="D110" s="18">
-        <f>D95-D96</f>
+        <f>D96+D97</f>
         <v/>
       </c>
       <c r="E110" s="18">
-        <f>E95-E96</f>
+        <f>E108+E109</f>
         <v/>
       </c>
       <c r="F110" s="18">
-        <f>F95-F96</f>
+        <f>F108+F109</f>
         <v/>
       </c>
       <c r="G110" s="18">
-        <f>G95-G96</f>
+        <f>G108+G109</f>
         <v/>
       </c>
       <c r="H110" s="18">
-        <f>H95-H96</f>
+        <f>H108+H109</f>
         <v/>
       </c>
       <c r="I110" s="18">
-        <f>I95-I96</f>
+        <f>I108+I109</f>
         <v/>
       </c>
       <c r="J110" s="18">
-        <f>J95-J96</f>
+        <f>J108+J109</f>
         <v/>
       </c>
       <c r="K110" s="18">
-        <f>K95-K96</f>
+        <f>K108+K109</f>
         <v/>
       </c>
       <c r="L110" s="18">
-        <f>L95-L96</f>
+        <f>L108+L109</f>
         <v/>
       </c>
       <c r="M110" s="18">
-        <f>M95-M96</f>
+        <f>M108+M109</f>
         <v/>
       </c>
       <c r="N110" s="18">
-        <f>N95-N96</f>
+        <f>N108+N109</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Ending</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>Beginning + Funding</t>
-        </is>
-      </c>
-      <c r="D111" s="18">
-        <f>D96+D97</f>
-        <v/>
-      </c>
-      <c r="E111" s="18">
-        <f>E96+E97</f>
-        <v/>
-      </c>
-      <c r="F111" s="18">
-        <f>F96+F97</f>
-        <v/>
-      </c>
-      <c r="G111" s="18">
-        <f>G96+G97</f>
-        <v/>
-      </c>
-      <c r="H111" s="18">
-        <f>H96+H97</f>
-        <v/>
-      </c>
-      <c r="I111" s="18">
-        <f>I96+I97</f>
-        <v/>
-      </c>
-      <c r="J111" s="18">
-        <f>J96+J97</f>
-        <v/>
-      </c>
-      <c r="K111" s="18">
-        <f>K96+K97</f>
-        <v/>
-      </c>
-      <c r="L111" s="18">
-        <f>L96+L97</f>
-        <v/>
-      </c>
-      <c r="M111" s="18">
-        <f>M96+M97</f>
-        <v/>
-      </c>
-      <c r="N111" s="18">
-        <f>N96+N97</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112"/>
+      <c r="A111" s="5" t="n"/>
+      <c r="B111" s="6" t="n"/>
+      <c r="C111" s="6" t="n"/>
+      <c r="D111" s="18" t="n"/>
+      <c r="E111" s="18" t="n"/>
+      <c r="F111" s="18" t="n"/>
+      <c r="G111" s="18" t="n"/>
+      <c r="H111" s="18" t="n"/>
+      <c r="I111" s="18" t="n"/>
+      <c r="J111" s="18" t="n"/>
+      <c r="K111" s="18" t="n"/>
+      <c r="L111" s="18" t="n"/>
+      <c r="M111" s="18" t="n"/>
+      <c r="N111" s="18" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTION WATERFALL</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="n"/>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="4" t="n"/>
+      <c r="H112" s="4" t="n"/>
+      <c r="I112" s="4" t="n"/>
+      <c r="J112" s="4" t="n"/>
+      <c r="K112" s="4" t="n"/>
+      <c r="L112" s="4" t="n"/>
+      <c r="M112" s="4" t="n"/>
+      <c r="N112" s="4" t="n"/>
+    </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTION WATERFALL</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="n"/>
-      <c r="C113" s="4" t="n"/>
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>Cash Available for Distribution</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>CFADS - Total DS - DSRA Fund</t>
+        </is>
+      </c>
       <c r="D113" s="4" t="n"/>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="4" t="n"/>
-      <c r="G113" s="4" t="n"/>
-      <c r="H113" s="4" t="n"/>
-      <c r="I113" s="4" t="n"/>
-      <c r="J113" s="4" t="n"/>
-      <c r="K113" s="4" t="n"/>
-      <c r="L113" s="4" t="n"/>
-      <c r="M113" s="4" t="n"/>
-      <c r="N113" s="4" t="n"/>
+      <c r="E113" s="18">
+        <f>E93-E97-E102-E109</f>
+        <v/>
+      </c>
+      <c r="F113" s="18">
+        <f>F93-F97-F102-F109</f>
+        <v/>
+      </c>
+      <c r="G113" s="18">
+        <f>G93-G97-G102-G109</f>
+        <v/>
+      </c>
+      <c r="H113" s="18">
+        <f>H93-H97-H102-H109</f>
+        <v/>
+      </c>
+      <c r="I113" s="18">
+        <f>I93-I97-I102-I109</f>
+        <v/>
+      </c>
+      <c r="J113" s="18">
+        <f>J93-J97-J102-J109</f>
+        <v/>
+      </c>
+      <c r="K113" s="18">
+        <f>K93-K97-K102-K109</f>
+        <v/>
+      </c>
+      <c r="L113" s="18">
+        <f>L93-L97-L102-L109</f>
+        <v/>
+      </c>
+      <c r="M113" s="18">
+        <f>M93-M97-M102-M109</f>
+        <v/>
+      </c>
+      <c r="N113" s="18">
+        <f>N93-N97-N102-N109</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Cash Available for Distribution</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+          <t>Lock-up Test</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="n"/>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>CFADS - Total DS - DSRA Fund</t>
-        </is>
-      </c>
-      <c r="E114" s="18">
-        <f>E81-(E85+E90)-E97</f>
-        <v/>
-      </c>
-      <c r="F114" s="18">
-        <f>F81-(F85+F90)-F97</f>
-        <v/>
-      </c>
-      <c r="G114" s="18">
-        <f>G81-(G85+G90)-G97</f>
-        <v/>
-      </c>
-      <c r="H114" s="18">
-        <f>H81-(H85+H90)-H97</f>
-        <v/>
-      </c>
-      <c r="I114" s="18">
-        <f>I81-(I85+I90)-I97</f>
-        <v/>
-      </c>
-      <c r="J114" s="18">
-        <f>J81-(J85+J90)-J97</f>
-        <v/>
-      </c>
-      <c r="K114" s="18">
-        <f>K81-(K85+K90)-K97</f>
-        <v/>
-      </c>
-      <c r="L114" s="18">
-        <f>L81-(L85+L90)-L97</f>
-        <v/>
-      </c>
-      <c r="M114" s="18">
-        <f>M81-(M85+M90)-M97</f>
-        <v/>
-      </c>
-      <c r="N114" s="18">
-        <f>N81-(N85+N90)-N97</f>
+          <t>PASS if DSCR ≥ Lock-up</t>
+        </is>
+      </c>
+      <c r="E114" s="22">
+        <f>IF(E104&gt;=$D$58,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="F114" s="22">
+        <f>IF(F104&gt;=$D$58,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="G114" s="22">
+        <f>IF(G104&gt;=$D$58,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H114" s="22">
+        <f>IF(H104&gt;=$D$58,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I114" s="22">
+        <f>IF(I104&gt;=$D$58,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J114" s="22">
+        <f>IF(J104&gt;=$D$58,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K114" s="22">
+        <f>IF(K104&gt;=$D$58,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L114" s="22">
+        <f>IF(L104&gt;=$D$58,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M114" s="22">
+        <f>IF(M104&gt;=$D$58,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N114" s="22">
+        <f>IF(N104&gt;=$D$58,"PASS","LOCKED")</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Lock-up Test</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr"/>
+          <t>Distributable Cash</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>PASS if DSCR ≥ Lock-up</t>
-        </is>
-      </c>
-      <c r="E115" s="22">
-        <f>IF(E92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="F115" s="22">
-        <f>IF(F92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="G115" s="22">
-        <f>IF(G92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="H115" s="22">
-        <f>IF(H92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="I115" s="22">
-        <f>IF(I92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="J115" s="22">
-        <f>IF(J92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="K115" s="22">
-        <f>IF(K92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="L115" s="22">
-        <f>IF(L92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="M115" s="22">
-        <f>IF(M92&gt;=$D$47,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="N115" s="22">
-        <f>IF(N92&gt;=$D$47,"PASS","LOCKED")</f>
+          <t>If PASS, MAX(0, Cash Avail)</t>
+        </is>
+      </c>
+      <c r="E115" s="7">
+        <f>IF(E114="PASS",MAX(0,E113),0)</f>
+        <v/>
+      </c>
+      <c r="F115" s="7">
+        <f>IF(F114="PASS",MAX(0,F113),0)</f>
+        <v/>
+      </c>
+      <c r="G115" s="7">
+        <f>IF(G114="PASS",MAX(0,G113),0)</f>
+        <v/>
+      </c>
+      <c r="H115" s="7">
+        <f>IF(H114="PASS",MAX(0,H113),0)</f>
+        <v/>
+      </c>
+      <c r="I115" s="7">
+        <f>IF(I114="PASS",MAX(0,I113),0)</f>
+        <v/>
+      </c>
+      <c r="J115" s="7">
+        <f>IF(J114="PASS",MAX(0,J113),0)</f>
+        <v/>
+      </c>
+      <c r="K115" s="7">
+        <f>IF(K114="PASS",MAX(0,K113),0)</f>
+        <v/>
+      </c>
+      <c r="L115" s="7">
+        <f>IF(L114="PASS",MAX(0,L113),0)</f>
+        <v/>
+      </c>
+      <c r="M115" s="7">
+        <f>IF(M114="PASS",MAX(0,M113),0)</f>
+        <v/>
+      </c>
+      <c r="N115" s="7">
+        <f>IF(N114="PASS",MAX(0,N113),0)</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>Distributable Cash</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>If PASS, MAX(0, Cash Avail)</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr"/>
-      <c r="F116" s="7" t="inlineStr"/>
-      <c r="G116" s="7" t="inlineStr"/>
-      <c r="H116" s="7" t="inlineStr"/>
-      <c r="I116" s="7" t="inlineStr"/>
-      <c r="J116" s="7" t="inlineStr"/>
-      <c r="K116" s="7" t="inlineStr"/>
-      <c r="L116" s="7" t="inlineStr"/>
-      <c r="M116" s="7" t="inlineStr"/>
-      <c r="N116" s="7" t="inlineStr"/>
-    </row>
-    <row r="117"/>
+      <c r="A116" s="5" t="n"/>
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="6" t="n"/>
+      <c r="E116" s="7" t="n"/>
+      <c r="F116" s="7" t="n"/>
+      <c r="G116" s="7" t="n"/>
+      <c r="H116" s="7" t="n"/>
+      <c r="I116" s="7" t="n"/>
+      <c r="J116" s="7" t="n"/>
+      <c r="K116" s="7" t="n"/>
+      <c r="L116" s="7" t="n"/>
+      <c r="M116" s="7" t="n"/>
+      <c r="N116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; USES (Year 0)</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="n"/>
+      <c r="C117" s="4" t="n"/>
+      <c r="D117" s="4" t="n"/>
+      <c r="E117" s="4" t="n"/>
+      <c r="F117" s="4" t="n"/>
+      <c r="G117" s="4" t="n"/>
+      <c r="H117" s="4" t="n"/>
+      <c r="I117" s="4" t="n"/>
+      <c r="J117" s="4" t="n"/>
+      <c r="K117" s="4" t="n"/>
+      <c r="L117" s="4" t="n"/>
+      <c r="M117" s="4" t="n"/>
+      <c r="N117" s="4" t="n"/>
+    </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>SOURCES &amp; USES (Year 0)</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="n"/>
-      <c r="C118" s="4" t="n"/>
+      <c r="A118" s="23" t="inlineStr">
+        <is>
+          <t>USES</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="n"/>
+      <c r="C118" s="6" t="n"/>
       <c r="D118" s="4" t="n"/>
       <c r="E118" s="4" t="n"/>
       <c r="F118" s="4" t="n"/>
@@ -5747,18 +5951,26 @@
       <c r="N118" s="4" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="23" t="inlineStr">
-        <is>
-          <t>USES</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr"/>
-      <c r="C119" s="6" t="inlineStr"/>
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Purchase Price</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="n"/>
+      <c r="D119" s="18">
+        <f>$D$28</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Purchase Price</t>
+          <t xml:space="preserve">  Transaction Fees</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
@@ -5766,16 +5978,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr"/>
+      <c r="C120" s="6" t="n"/>
       <c r="D120" s="18">
-        <f>$D$17</f>
+        <f>$D$28*$D$29</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Transaction Fees</t>
+          <t xml:space="preserve">  DSRA Funding</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
@@ -5783,16 +5995,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr"/>
+      <c r="C121" s="6" t="n"/>
       <c r="D121" s="18">
-        <f>$D$17*$D$18</f>
+        <f>E107</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DSRA Funding</t>
+          <t>Total Uses</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
@@ -5800,43 +6012,48 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr"/>
-      <c r="D122" s="18">
-        <f>D95</f>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="7">
+        <f>D119+D120+D121</f>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>Total Uses</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr"/>
-      <c r="D123" s="7">
-        <f>D107+D108+D109</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124"/>
+      <c r="A123" s="5" t="n"/>
+      <c r="B123" s="6" t="n"/>
+      <c r="C123" s="6" t="n"/>
+      <c r="D123" s="7" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="23" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="n"/>
+      <c r="C124" s="6" t="n"/>
+    </row>
     <row r="125">
-      <c r="A125" s="23" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr"/>
-      <c r="C125" s="6" t="inlineStr"/>
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Debt</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="18">
+        <f>$D$28*$D$53</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Debt</t>
+          <t xml:space="preserve">  Equity</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
@@ -5844,16 +6061,20 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr"/>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>Plug to balance</t>
+        </is>
+      </c>
       <c r="D126" s="18">
-        <f>$D$57</f>
+        <f>D122-D125</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Equity</t>
+          <t>Total Sources</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
@@ -5861,63 +6082,81 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>Plug to balance</t>
-        </is>
-      </c>
-      <c r="D127" s="18">
-        <f>D110-D113</f>
+      <c r="C127" s="6" t="n"/>
+      <c r="D127" s="7">
+        <f>D125+D126</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Total Sources</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr"/>
-      <c r="D128" s="7">
-        <f>D113+D114</f>
+          <t>Balance Check</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="n"/>
+      <c r="C128" s="6" t="n"/>
+      <c r="D128" s="10">
+        <f>IF(ABS(D122-D127)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>Balance Check</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr"/>
-      <c r="C129" s="6" t="inlineStr"/>
-      <c r="D129" s="10">
-        <f>IF(ABS(D110-D115)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130"/>
+      <c r="A129" s="5" t="n"/>
+      <c r="B129" s="6" t="n"/>
+      <c r="C129" s="6" t="n"/>
+      <c r="D129" s="10" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>EXIT CALCULATIONS</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="n"/>
+      <c r="C130" s="4" t="n"/>
+      <c r="D130" s="4" t="n"/>
+      <c r="E130" s="4" t="n"/>
+      <c r="F130" s="4" t="n"/>
+      <c r="G130" s="4" t="n"/>
+      <c r="H130" s="4" t="n"/>
+      <c r="I130" s="4" t="n"/>
+      <c r="J130" s="4" t="n"/>
+      <c r="K130" s="4" t="n"/>
+      <c r="L130" s="4" t="n"/>
+      <c r="M130" s="4" t="n"/>
+      <c r="N130" s="4" t="n"/>
+    </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>EXIT CALCULATIONS</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="n"/>
-      <c r="C131" s="4" t="n"/>
-      <c r="D131" s="4" t="n"/>
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>Exit EV</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>Exit Multiple × Exit Yr EBITDA</t>
+        </is>
+      </c>
+      <c r="D131" s="4">
+        <f>K87*$D$30</f>
+        <v/>
+      </c>
       <c r="E131" s="4" t="n"/>
       <c r="F131" s="4" t="n"/>
       <c r="G131" s="4" t="n"/>
       <c r="H131" s="4" t="n"/>
       <c r="I131" s="4" t="n"/>
       <c r="J131" s="4" t="n"/>
-      <c r="K131" s="4" t="n"/>
+      <c r="K131" s="18">
+        <f>$D$19*K75</f>
+        <v/>
+      </c>
       <c r="L131" s="4" t="n"/>
       <c r="M131" s="4" t="n"/>
       <c r="N131" s="4" t="n"/>
@@ -5925,7 +6164,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Exit EV</t>
+          <t>Exit Debt Payoff</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
@@ -5935,15 +6174,22 @@
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Exit Multiple × Exit Yr EBITDA</t>
-        </is>
-      </c>
-      <c r="K132" s="18" t="inlineStr"/>
+          <t>Ending Bal at Exit</t>
+        </is>
+      </c>
+      <c r="D132">
+        <f>K103</f>
+        <v/>
+      </c>
+      <c r="K132" s="18">
+        <f>K91</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Exit Debt Payoff</t>
+          <t>DSRA Release</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
@@ -5953,18 +6199,22 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Ending Bal at Exit</t>
-        </is>
+          <t>DSRA Ending at Exit</t>
+        </is>
+      </c>
+      <c r="D133">
+        <f>K110</f>
+        <v/>
       </c>
       <c r="K133" s="18">
-        <f>K91</f>
+        <f>K98</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>DSRA Release</t>
+          <t>Exit Equity Proceeds</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
@@ -5974,190 +6224,266 @@
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>DSRA Ending at Exit</t>
-        </is>
-      </c>
-      <c r="K134" s="18">
-        <f>K98</f>
+          <t>Exit EV - Debt + DSRA</t>
+        </is>
+      </c>
+      <c r="D134">
+        <f>D131-D132+D133</f>
+        <v/>
+      </c>
+      <c r="K134" s="7">
+        <f>K119-K120+K121</f>
         <v/>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Exit Equity Proceeds</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>Exit EV - Debt + DSRA</t>
-        </is>
-      </c>
-      <c r="K135" s="7" t="inlineStr"/>
-    </row>
-    <row r="136"/>
+      <c r="A135" s="5" t="n"/>
+      <c r="B135" s="6" t="n"/>
+      <c r="C135" s="6" t="n"/>
+      <c r="K135" s="7" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>EQUITY RETURNS</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="4" t="n"/>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="4" t="n"/>
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="4" t="n"/>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="n"/>
+      <c r="J136" s="4" t="n"/>
+      <c r="K136" s="4" t="n"/>
+      <c r="L136" s="4" t="n"/>
+      <c r="M136" s="4" t="n"/>
+      <c r="N136" s="4" t="n"/>
+    </row>
     <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>EQUITY RETURNS</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="n"/>
-      <c r="C137" s="4" t="n"/>
-      <c r="D137" s="4" t="n"/>
-      <c r="E137" s="4" t="n"/>
-      <c r="F137" s="4" t="n"/>
-      <c r="G137" s="4" t="n"/>
-      <c r="H137" s="4" t="n"/>
-      <c r="I137" s="4" t="n"/>
-      <c r="J137" s="4" t="n"/>
-      <c r="K137" s="4" t="n"/>
-      <c r="L137" s="4" t="n"/>
-      <c r="M137" s="4" t="n"/>
-      <c r="N137" s="4" t="n"/>
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Equity Cash Flow</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="n"/>
+      <c r="D137" s="18">
+        <f>-D126</f>
+        <v/>
+      </c>
+      <c r="E137" s="18">
+        <f>E115</f>
+        <v/>
+      </c>
+      <c r="F137" s="18">
+        <f>F115</f>
+        <v/>
+      </c>
+      <c r="G137" s="18">
+        <f>G115</f>
+        <v/>
+      </c>
+      <c r="H137" s="18">
+        <f>H115</f>
+        <v/>
+      </c>
+      <c r="I137" s="18">
+        <f>I115</f>
+        <v/>
+      </c>
+      <c r="J137" s="18">
+        <f>J115</f>
+        <v/>
+      </c>
+      <c r="K137" s="18">
+        <f>K115+D134</f>
+        <v/>
+      </c>
+      <c r="L137" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Equity Cash Flow</t>
+          <t>Levered IRR</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr"/>
-      <c r="D138" s="18" t="inlineStr"/>
-      <c r="E138" s="18" t="inlineStr"/>
-      <c r="F138" s="18" t="inlineStr"/>
-      <c r="G138" s="18" t="inlineStr"/>
-      <c r="H138" s="18" t="inlineStr"/>
-      <c r="I138" s="18" t="inlineStr"/>
-      <c r="J138" s="18" t="inlineStr"/>
-      <c r="K138" s="18" t="inlineStr"/>
-      <c r="L138" s="18" t="inlineStr"/>
-      <c r="M138" s="18" t="inlineStr"/>
-      <c r="N138" s="18" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
+      </c>
+      <c r="D138" s="31" t="n"/>
+      <c r="E138" s="18" t="n"/>
+      <c r="F138" s="18" t="n"/>
+      <c r="G138" s="18" t="n"/>
+      <c r="H138" s="18" t="n"/>
+      <c r="I138" s="18" t="n"/>
+      <c r="J138" s="18" t="n"/>
+      <c r="K138" s="18" t="n"/>
+      <c r="L138" s="18" t="n"/>
+      <c r="M138" s="18" t="n"/>
+      <c r="N138" s="18" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
+          <t>MOIC</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr"/>
-      <c r="D139" s="31" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Sum inflows / outflow</t>
+        </is>
+      </c>
+      <c r="D139" s="30" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>Sum inflows / outflow</t>
-        </is>
-      </c>
-      <c r="D140" s="30" t="inlineStr"/>
-    </row>
-    <row r="141"/>
+      <c r="A140" s="5" t="n"/>
+      <c r="B140" s="6" t="n"/>
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="30" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="23" t="inlineStr">
+        <is>
+          <t>Unlevered Returns (for reference)</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="n"/>
+      <c r="C141" s="6" t="n"/>
+    </row>
     <row r="142">
-      <c r="A142" s="23" t="inlineStr">
-        <is>
-          <t>Unlevered Returns (for reference)</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr"/>
-      <c r="C142" s="6" t="inlineStr"/>
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="n"/>
+      <c r="D142" s="18">
+        <f>-$D$28-D120</f>
+        <v/>
+      </c>
+      <c r="E142" s="18">
+        <f>E93</f>
+        <v/>
+      </c>
+      <c r="F142" s="18">
+        <f>F93</f>
+        <v/>
+      </c>
+      <c r="G142" s="18">
+        <f>G93</f>
+        <v/>
+      </c>
+      <c r="H142" s="18">
+        <f>H93</f>
+        <v/>
+      </c>
+      <c r="I142" s="18">
+        <f>I93</f>
+        <v/>
+      </c>
+      <c r="J142" s="18">
+        <f>J93</f>
+        <v/>
+      </c>
+      <c r="K142" s="18">
+        <f>K93+D131</f>
+        <v/>
+      </c>
+      <c r="L142" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Unlevered Cash Flow</t>
+          <t>Unlevered IRR</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr"/>
-      <c r="D143" s="18">
-        <f>-$D$17-D108</f>
-        <v/>
-      </c>
-      <c r="E143" s="18">
-        <f>E81</f>
-        <v/>
-      </c>
-      <c r="F143" s="18">
-        <f>F81</f>
-        <v/>
-      </c>
-      <c r="G143" s="18">
-        <f>G81</f>
-        <v/>
-      </c>
-      <c r="H143" s="18">
-        <f>H81</f>
-        <v/>
-      </c>
-      <c r="I143" s="18">
-        <f>I81</f>
-        <v/>
-      </c>
-      <c r="J143" s="18">
-        <f>J81</f>
-        <v/>
-      </c>
-      <c r="K143" s="18">
-        <f>K81+K119</f>
-        <v/>
-      </c>
-      <c r="L143" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M143" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N143" s="18">
-        <f>0</f>
-        <v/>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
+      </c>
+      <c r="D143" s="31">
+        <f>IRR(D142:N142)</f>
+        <v/>
+      </c>
+      <c r="E143" s="18" t="n"/>
+      <c r="F143" s="18" t="n"/>
+      <c r="G143" s="18" t="n"/>
+      <c r="H143" s="18" t="n"/>
+      <c r="I143" s="18" t="n"/>
+      <c r="J143" s="18" t="n"/>
+      <c r="K143" s="18" t="n"/>
+      <c r="L143" s="18" t="n"/>
+      <c r="M143" s="18" t="n"/>
+      <c r="N143" s="18" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr"/>
-      <c r="D144" s="31" t="inlineStr"/>
-    </row>
+      <c r="A144" s="5" t="n"/>
+      <c r="B144" s="6" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="31" t="n"/>
+    </row>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
@@ -3026,7 +3026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3447,7 +3447,7 @@
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="10">
-        <f>IF(K91&lt;1,"PASS","FAIL")</f>
+        <f>IF(K103&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -3474,7 +3474,6 @@
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="10" t="n"/>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -6468,22 +6467,6 @@
       <c r="C144" s="6" t="n"/>
       <c r="D144" s="31" t="n"/>
     </row>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
@@ -3423,10 +3423,7 @@
       </c>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
-      <c r="D22" s="10">
-        <f>D116</f>
-        <v/>
-      </c>
+      <c r="D22" s="10" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
@@ -3464,7 +3461,7 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
+        <f>IF(MINIFS(E104:K104,E104:K104,"&gt;0")&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_2_Peaker.xlsx
@@ -162,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -243,6 +243,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3204,10 +3205,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="n"/>
-      <c r="B6" s="49" t="n"/>
-      <c r="C6" s="49" t="n"/>
-      <c r="D6" s="49" t="n"/>
+      <c r="A6" s="49" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="B6" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>Minimum debt service coverage ratio</t>
+        </is>
+      </c>
+      <c r="D6" s="60">
+        <f>IF(COUNTIF(E104:K104,"&gt;0")&gt;0,MINIFS(E104:K104,E104:K104,"&gt;0"),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="50" t="inlineStr">
@@ -3461,7 +3477,7 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>IF(MINIFS(E104:K104,E104:K104,"&gt;0")&gt;=1.25,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
